--- a/agliluz/historial_licitaciones.xlsx
+++ b/agliluz/historial_licitaciones.xlsx
@@ -518,20 +518,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1057472-84-LP26</t>
+          <t>1057472-9-LP26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CONVENIO DE MANTENIMIENTO PARA AUTOCLAVE STERRAD</t>
+          <t>CONVENIO DE MANTENIMIENTO TOMÓGRAFO COMPUTARIZADO</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-07T16:00:00</t>
+          <t>2026-08-18T16:00:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -599,20 +599,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1150-14-O126</t>
+          <t>1263503-3-O126</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Conservación Cauces Naturales Rio Clarillo 2026</t>
+          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA III</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-03T11:05:52.27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -680,20 +680,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1211839-53-LE26</t>
+          <t>1057472-84-LP26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE MATERIALES E IMPLEMENTOS DEPORTIVOS</t>
+          <t>CONVENIO DE MANTENIMIENTO PARA AUTOCLAVE STERRAD</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-07-07T16:00:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -761,20 +761,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1057472-85-LP26</t>
+          <t>1150-14-O126</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CONVENIO MANTENIMIENTO EQUIPOS Y TORRES ENDOSCOPIA</t>
+          <t>Conservación Cauces Naturales Rio Clarillo 2026</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-07T16:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -842,20 +842,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1225288-5-LE26</t>
+          <t>1211839-53-LE26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IMPLEMENTACIÓN PARA APOYO CLUBES DEPORTIVOS</t>
+          <t>ADQUISICIÓN DE MATERIALES E IMPLEMENTOS DEPORTIVOS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-26T16:30:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -923,20 +923,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1233616-49-LE26</t>
+          <t>2186-21-LE26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO IMPRESORAS Y MULTIFUNCIONALES EE.EE</t>
+          <t>MANTENIMIENTO PREVENTIVO PARA CALDERAS</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-18T12:00:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1004,12 +1004,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1233616-51-L126</t>
+          <t>1263503-2-O126</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO TORRES DE COMUNICACIÓN ARRIOSTRADA</t>
+          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA II</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-03T15:04:02.473</t>
+          <t>2026-08-03T11:03:43.517</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1328,20 +1328,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1798-5-LE26</t>
+          <t>1048-55-LE26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Servicio de Mantenimiento de Red eléctrica y otros</t>
+          <t>ADQ. VESTUARIO Y EPP PERSONAL LUMINARIA 2do LLAMAD</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-24T15:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1409,12 +1409,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1951-31-LE26</t>
+          <t>1063538-165-LP26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO CORRECTIVO EQUIPOS REFRIG</t>
+          <t>CONVENIO MANTENIMIENTO DE EQUIPOS MEDICOS</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-03T15:31:00</t>
+          <t>2026-08-03T16:15:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1490,20 +1490,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2322-53-LR26</t>
+          <t>1063538-185-LP26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construcción Cancha de Pasto Sintetico Meseta Azul  Vallenar </t>
+          <t>MANTENIMIENTO SISTEMA GASES CLINICOS</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-08-14T15:15:00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1519,12 +1519,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1571,12 +1571,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2328-44-LE26</t>
+          <t>1344402-6-E226</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA E-472026 “ADQUISICION DE MATERIALES ELECTRICOS PARA LA ESPECIALIDAD DE ELECTRICIDAD TP 2024 LICEO INDUSTRIAL PUERTO MONTT”</t>
+          <t>MANTENCIÓN Y DIAGNÓSTICO CÁMARAS DE CONSERVACIÓN</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-03T15:03:00</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1652,12 +1652,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2342-30-LP26</t>
+          <t>2332-78-L126</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO MULTICANCHAS CASAS DEL PARQUE III LA PORTADA Y CONSTRUCCIÓN SANTA BÁRBARA SAN BERNARDO</t>
+          <t>SERVICIOS DE CONSERVACIÓN DE INFRAESTRUCTURA DEL SAR ALERCE</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1681,12 +1681,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1733,12 +1733,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2744-26-L126</t>
+          <t>2345-127-LE26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO INTEGRAL DE AUTOCLAVE</t>
+          <t>ADQUISICIÓN DE ARTÍCULOS DEPORTIVOS</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-10T15:47:00</t>
+          <t>2026-08-17T15:01:00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1814,20 +1814,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3326-35-LE26</t>
+          <t>2765-44-E226</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN E INSTALACIÓN DE ACCESORIO PARA EL VEHÍCULO FISCAL AC-2429 MARCA NISSAN MODELO PATHFINDER AÑO 2026 DE CARGO DE LA SUBDIRECCIÓN GENERAL SEGÚN BASES ADMINISTRATIVAS Y TÉCNICAS</t>
+          <t>SERVICIO DE MANTENIMIENTO CENTRO COMUNITARIO SERGI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-03T18:03:05.86</t>
+          <t>2026-08-10T16:23:00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1895,20 +1895,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3399-17-L126</t>
+          <t>3390-21-LE26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Servicio de mantenimiento para el mini bus Merces Benz Sprinter del Regimiento N° 16 Talca.</t>
+          <t>Materiales para Mantenimiento y Reparaciones.</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-30T15:56:00</t>
+          <t>2026-08-03T15:57:00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1976,20 +1976,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3296-19-LE25</t>
+          <t>3562-28-LR26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Contratación AITO conservación camino no enrolados 8 sectores rurales Curaco de Vélez.</t>
+          <t>CONSERVACIÓN COMPLEJO DEPORTIVO ESPERANZA CALERA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-01-08T19:55:00</t>
+          <t>2026-09-03T16:37:00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2005,12 +2005,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Certificación SEC (Chile)</t>
+          <t>Normativa estándar de licitación</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2057,20 +2057,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1186-2-LE26</t>
+          <t>1389488-17-LP26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO DE ASCENSORES</t>
+          <t xml:space="preserve">SUMINISTRO DE INDUMENTARIA ARTÍCULOS DEPORTIVOS   </t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-13T15:00:00</t>
+          <t>2026-06-04T16:37:00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2138,20 +2138,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1225288-2-LE26</t>
+          <t>1658-151-LP26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IMPLEMENTACIÓN TALLERES DEPORTIVOS RECREATIVOS</t>
+          <t>P.168-2026 OBRAS DE IMPERMEABILIZACIÓN DE GRADERÍAS TRIBUNA PACÍFICO ESTADIO MUNICIPAL GERMÁN BECKER TEMUCO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-26T16:30:00</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2219,20 +2219,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1263503-1-O126</t>
+          <t>2403-52-LP26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA I</t>
+          <t>Reposición calzada pasaje Maracaibo</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-03T10:51:48.64</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2300,12 +2300,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1306643-23-LE26</t>
+          <t>2744-26-L126</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SERVICIO DE REPOSICIÓN MAMPARAS CESFAM</t>
+          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO INTEGRAL DE AUTOCLAVE</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-18T15:00:00</t>
+          <t>2026-08-10T15:47:00</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2381,20 +2381,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1048-55-LE26</t>
+          <t>3326-35-LE26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ADQ. VESTUARIO Y EPP PERSONAL LUMINARIA 2do LLAMAD</t>
+          <t>ADQUISICIÓN E INSTALACIÓN DE ACCESORIO PARA EL VEHÍCULO FISCAL AC-2429 MARCA NISSAN MODELO PATHFINDER AÑO 2026 DE CARGO DE LA SUBDIRECCIÓN GENERAL SEGÚN BASES ADMINISTRATIVAS Y TÉCNICAS</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-03T18:03:05.86</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2462,12 +2462,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1063538-165-LP26</t>
+          <t>2328-43-LE26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CONVENIO MANTENIMIENTO DE EQUIPOS MEDICOS</t>
+          <t>LICITACIÓN PÚBLICA E-502026  “ADQUISICION DE EQUIPAMIENTO PARA LA ESPECIALIDAD DE MECANICA INDUSTRIAL DEL LICEO INDUSTRIAL PUERTO MONTT FONDO TP 2024”</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-03T16:15:00</t>
+          <t>2026-08-03T15:52:00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2543,12 +2543,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1063538-185-LP26</t>
+          <t>1186-2-LE26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO SISTEMA GASES CLINICOS</t>
+          <t>SERVICIO DE MANTENIMIENTO DE ASCENSORES</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-14T15:15:00</t>
+          <t>2026-08-13T15:00:00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2624,20 +2624,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1344402-6-E226</t>
+          <t>1225288-2-LE26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MANTENCIÓN Y DIAGNÓSTICO CÁMARAS DE CONSERVACIÓN</t>
+          <t>IMPLEMENTACIÓN TALLERES DEPORTIVOS RECREATIVOS</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-06-26T16:30:00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2653,12 +2653,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2705,20 +2705,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1057472-9-LP26</t>
+          <t>1263503-1-O126</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CONVENIO DE MANTENIMIENTO TOMÓGRAFO COMPUTARIZADO</t>
+          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA I</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-18T16:00:00</t>
+          <t>2026-08-03T10:51:48.64</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2786,20 +2786,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1263503-3-O126</t>
+          <t>1306643-23-LE26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA III</t>
+          <t>SERVICIO DE REPOSICIÓN MAMPARAS CESFAM</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-08-03T11:05:52.27</t>
+          <t>2026-08-18T15:00:00</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2867,20 +2867,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3482-6-LE26</t>
+          <t>2788-33-LP26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mantenimiento y Reparación de Baño.</t>
+          <t>REPOSICIÓN MULTICANCHA VILLA LAS AMÉRICAS I PAINE</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-08-10T16:00:00</t>
+          <t>2026-08-03T15:01:00</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2948,20 +2948,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4483-15-LR26</t>
+          <t>3565-54-LE26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>REPOSICION CUARTEL GENERAL 1° COMPAÑIA DE BOMBEROS TIERRA AMARILLA</t>
+          <t>MATRERIALES PARA REPOSICION PASARELAS</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-30T15:30:00</t>
+          <t>2026-08-14T12:24:00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3029,12 +3029,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4494-47-LE26</t>
+          <t>4412-20-LP26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN ESCUELA EDUARDO CAMPBELL PENCO</t>
+          <t>MEJORAMIENTO MULTICANCHAS EL RETIRO Y TUCUQUERE</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-08-18T15:00:00</t>
+          <t>2026-09-02T15:30:00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3110,20 +3110,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>584264-35-LR26</t>
+          <t>5908-25-LP26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SUM.SEÑALES DE TRANSITO DEMARCACIÓN INDEPENDENCIA</t>
+          <t>REPOSICIÓN ESCALERAS PÚBLICAS LOCALIDAD DE SIBAYA COMUNA DE HUARA</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-04T15:05:00</t>
+          <t>2026-08-03T16:00:00</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3139,12 +3139,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3191,20 +3191,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>608897-45-LE26</t>
+          <t>3399-17-L126</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SISTEMATIZACIÓN DE INFORMACIÓN PARA LA IDENTIFICACIÓN DE PRIORIDADES DE CONSERVACIÓN MARINA PARA EL DISEÑO DE UNA RED DE ÁREAS MARINAS PROTEGIDAS EN LAS ECORREGIONES HUMBOLDTIANA CHILE CENTRAL ARAUCANA CHILOENSE Y CANALESFIORDOS DEL SUR DE CHILE</t>
+          <t>Servicio de mantenimiento para el mini bus Merces Benz Sprinter del Regimiento N° 16 Talca.</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-13T16:00:00</t>
+          <t>2026-07-30T15:56:00</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3272,12 +3272,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>610-13-LP26</t>
+          <t>3482-6-LE26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Determinación del Estándar Metodológico para el Cálculo de Rotura y Reposición de Pavimentos en Redes de Distribución</t>
+          <t>Mantenimiento y Reparación de Baño.</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-08-21T15:00:00</t>
+          <t>2026-08-10T16:00:00</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3353,20 +3353,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2274-30-LE26</t>
+          <t>1057472-85-LP26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PROPUESTA PUBLICA ADQUISICION MATERIAL DE ENSEÑANZA E INSUMOS DEPORTIVOS CONVENIO LA PINTANA 2026 EXP. 11856</t>
+          <t>CONVENIO MANTENIMIENTO EQUIPOS Y TORRES ENDOSCOPIA</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-03T18:40:00</t>
+          <t>2026-07-07T16:00:00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3434,20 +3434,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2328-46-LE26</t>
+          <t>1225288-5-LE26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA E-55 ADQUISICION DE CALZADO DEPORTIVO JARDINES INFANTILES DEPENDIENTES DEL DAEM DE PUERTO MONTT</t>
+          <t>IMPLEMENTACIÓN PARA APOYO CLUBES DEPORTIVOS</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-06-26T16:30:00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3515,20 +3515,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1263503-2-O126</t>
+          <t>1233616-49-LE26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA II</t>
+          <t>MANTENIMIENTO IMPRESORAS Y MULTIFUNCIONALES EE.EE</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-08-03T11:03:43.517</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3596,20 +3596,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2328-43-LE26</t>
+          <t>1233616-51-L126</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA E-502026  “ADQUISICION DE EQUIPAMIENTO PARA LA ESPECIALIDAD DE MECANICA INDUSTRIAL DEL LICEO INDUSTRIAL PUERTO MONTT FONDO TP 2024”</t>
+          <t>MANTENIMIENTO TORRES DE COMUNICACIÓN ARRIOSTRADA</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-03T15:52:00</t>
+          <t>2026-08-03T15:04:02.473</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3677,20 +3677,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1057472-87-LP26</t>
+          <t>1085111-21-LR26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CONVENIO DE MANTENIMIENTO PARA LAVACHATAS MEIKO</t>
+          <t>CONSERVACIÓN MANT Y SEG PARQUE MONUM CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-07T16:00:00</t>
+          <t>2026-08-03T16:00:00</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3758,20 +3758,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1133353-35-LP26</t>
+          <t>1133353-34-LE26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE MATERIALES DE CONSTRUCCIÓN PARA MANTENIMIENTO DE EDIFICIOS MUNICIPALES EMERGENCIA Y APOYO SOCIAL DE LA MUNICIPALIDAD DE RAUCO</t>
+          <t>MECANICA DE SUELOS PROYECTO CONSTRUCCION POLIDEPORTIVO RAUCO</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-08-13T17:30:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3839,12 +3839,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1198-24-LE26</t>
+          <t>1232565-25-L126</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mantención y Obras Menores Estadio San Felipe</t>
+          <t>Adquisición de Equipamiento Deportivos Proyecto ULS 2595</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-13T15:00:00</t>
+          <t>2026-08-10T17:00:00</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3920,20 +3920,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1199-11-LE26</t>
+          <t>1263503-4-O126</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mantener y Reparar Aire acondicionado IND MAULE</t>
+          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA IV</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-03T17:00:00</t>
+          <t>2026-08-03T11:07:24.06</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4001,20 +4001,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1369-14-O126</t>
+          <t>3080-2-L126</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONSERVACIÓN CAMINOS BÁSICOS B-383, CRUCE 23 CH, LAGUNA MISCANTI, PROV. EL </t>
+          <t xml:space="preserve">ADQUISICIÓN DE SERVICIO POR REPARACIÓN Y MANTENIMIENTO EDIFICIO MICALVI </t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-07T18:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4082,20 +4082,20 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1481-5-L126</t>
+          <t>3436-86-L126</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>COMPRA DE ARTICULOS DE LIBRERIA, MATERIAL PEDAGOGICO, DEPORTIVO, ALIMENTACION Y ASEO SAAT - INSTITUTO DE EDUCACION PARA EL ADULTO RBD 40008-4</t>
+          <t>Mantenimiento de equipos de rancho Ítem 22.06.999 SIC 349184</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-22T15:00:00</t>
+          <t>2026-08-03T15:10:00</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4163,20 +4163,20 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2467-79-LE26</t>
+          <t>3562-31-LR26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE CAMARAS DE SEGURIDAD PARA RECAMBIO</t>
+          <t>CONSERVACIÓN ESTADIO DE PUEBLO NUEVO LA CALERA</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-08-03T15:20:00</t>
+          <t>2026-09-03T16:00:00</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4244,12 +4244,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2760-100-LE26</t>
+          <t>359-91-LE26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PRODUCCION Y DESARROLLO DE EVENTOS JORNADA FAMILIAR INTERACTIVA DE LOS DERECHOS DE LAS NIÑAS Y NIÑOS 2026</t>
+          <t>ADECUACIÓN DE RECINTOS PARA INSTALACIÓN DE TOMÓGRAFO COMPUTARIZADO EN EL INSTITUTO NACIONAL DEL CÁNCER</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-03T16:00:00</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4318,27 +4318,27 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>Plataforma Interact</t>
+          <t>Sin requerimientos de control específicos</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2793-104-LE26</t>
+          <t>3938-25-LE26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE EQUIPOS Y SISTEMAS CLIMATIZACION</t>
+          <t>Mejoramiento Cierre Perimetral Recinto Deportivo Catripulli</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-03T15:01:00</t>
+          <t>2026-08-21T16:20:00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4406,20 +4406,20 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2981-204-LE26</t>
+          <t>3968-35-LE26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO DE CALDERAS</t>
+          <t>UNIFORMES DEPORTIVOS ESC. MONSEÑOR MANUEL LARRAIN</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-14T15:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4487,20 +4487,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3084-15-R126</t>
+          <t>4118-5-LP26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE LICENCIAS OFFICE LTSC PRO PLUS 2024 LICENCIAS MICROSOFT WINDOWS 11 PRO LICENCIAS WINDOWS EXCHANGE SERVER 2019 LICENCIAS WINDOWS SERVER 2025 STANDARD 16 CORES ESP Y LICENCIAS EXCHANGE SERVER STANDARD 2019 CAL SU EQUIVALENTE TÉCNICO O SU</t>
+          <t>ALUMBRADO PÚBLICO SECTOR COMUNA SANTA INÉS</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-06-03T15:00:00</t>
+          <t>2026-08-25T12:00:00</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -4568,20 +4568,20 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3621-39-LE26</t>
+          <t>618472-3-L126</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>INSTALACION DE ALUMBRADO PUBLICO ORNAMENTAL PASEO</t>
+          <t>Servicio de mantenimiento, reparación y repuestos de Aire Acondicionado.</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-03T16:20:00</t>
+          <t>2026-08-12T08:00:00</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4649,12 +4649,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3693-141-CO26</t>
+          <t>707426-25-LP26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN Y HABILITACIÓN SALAS DE BOMBAS COMPLEJO EDUCACIONAL CLARA SOLOVERA COLEGIO EL QUISCO Y ESCUELA POETA NERUDA</t>
+          <t>REPOSICIÓN CUBIERTA Y SIST. ELECT. JI TIA NORA.</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -4730,20 +4730,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>407-86-LE26</t>
+          <t>740-12-LE26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO PREVENTIVO Y REPARATIVO SIN REPUESTOS PARA AUTOCLAVE</t>
+          <t>SERVICIO DE CATERING EN LA REGIÓN DEL MAULE INDAP</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-03T10:53:14.54</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4811,20 +4811,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2186-21-LE26</t>
+          <t>761391-107-L126</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO PARA CALDERAS</t>
+          <t>DE/56/GUB/CURSO DE MANTENIMIENTO DE SISTEMAS DE REFRIGERACIÓN Y MANTENIMIENTO DE CALDERAS</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-18T12:00:00</t>
+          <t>2026-07-21T15:00:00</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4892,20 +4892,20 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2332-78-L126</t>
+          <t>802-11-LE26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SERVICIOS DE CONSERVACIÓN DE INFRAESTRUCTURA DEL SAR ALERCE</t>
+          <t>Difusión y validación de un programa de Magíster en lengua y cultura indígena</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-06-23T10:00:00</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4973,20 +4973,20 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3296-1-LE26</t>
+          <t>826-11-O126</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Contratación AITO conservación camino no enrolados 4 sectores rurales Curaco de Vélez.</t>
+          <t>AIF OBRA REPOSICIÓN CONSULTORIO LAUTARO Y ADECUACIÓN A CESFAM</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-01-16T09:00:00</t>
+          <t>2026-08-19T09:00:00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Certificación SEC (Chile)</t>
+          <t>Normativa estándar de licitación</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -5054,20 +5054,20 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2345-127-LE26</t>
+          <t>2274-30-LE26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ARTÍCULOS DEPORTIVOS</t>
+          <t>PROPUESTA PUBLICA ADQUISICION MATERIAL DE ENSEÑANZA E INSUMOS DEPORTIVOS CONVENIO LA PINTANA 2026 EXP. 11856</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-17T15:01:00</t>
+          <t>2026-08-03T18:40:00</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5135,20 +5135,20 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2765-44-E226</t>
+          <t>2328-46-LE26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO CENTRO COMUNITARIO SERGI</t>
+          <t>LICITACIÓN PÚBLICA E-55 ADQUISICION DE CALZADO DEPORTIVO JARDINES INFANTILES DEPENDIENTES DEL DAEM DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-10T16:23:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5164,12 +5164,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5216,20 +5216,20 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3390-21-LE26</t>
+          <t>4261-4-LE26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Materiales para Mantenimiento y Reparaciones.</t>
+          <t>MTS Conservación CDI España Comuna de Angol</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-03T15:57:00</t>
+          <t>2026-08-03T16:20:14.27</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5297,20 +5297,20 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3562-28-LR26</t>
+          <t>545598-24-LE26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN COMPLEJO DEPORTIVO ESPERANZA CALERA</t>
+          <t>CONVENIO DE SUMINISTRO DE OXÍGENO MEDICINAL Y GASES CLÍNICOS CON CILINDROS EN ARRIENDO</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-03T16:37:00</t>
+          <t>2026-07-17T15:04:00</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5378,12 +5378,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>633-43-L126</t>
+          <t>584105-14-LP26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CURSO DE CAPACITACIÓN EN PUEBLOS INDÍGENAS</t>
+          <t>INCORPORACIÓN COMPONENTE INDÍGENA EN LA PLANIFICACIÓN ENERGÉTICA Y RESILIENCIA ENERGÉTICA EN RAPA NUI EN CUMPLIMIENTO CON EL PLAN SECTORIAL DE MITIGACIÓN Y DE ADAPTACIÓN AL CAMBIO CLIMÁTICO EN ENERGÍA</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-10T19:00:00</t>
+          <t>2026-08-24T15:01:00</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -5459,20 +5459,20 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>750998-47-LP26</t>
+          <t>673663-15-LP26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>REPOSICIÓN CANCHA DE BABY FUTBOL CD LOS 56 UNIDOS</t>
+          <t>CONSTRUCCIÓN RED ALUMBRADO PÚBLICO Y LUMINARIAS SO</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-03T15:15:00</t>
+          <t>2026-08-03T13:18:45.21</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5488,12 +5488,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5540,20 +5540,20 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>934-11-LE26</t>
+          <t>697057-29-LE26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SERVICIO DE GUARDIAS IND REGION DE LOS LAGOS</t>
+          <t>Reposición cubierta de la Fiscalía de Pichilemu</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-09-03T11:00:00</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5621,12 +5621,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>935-17-LE26</t>
+          <t>1434-21-LE26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>INDUMENTARIA DEPORTIVA SNCD IND XII REGION</t>
+          <t>MANTENIMIENTO DE EQUIPOS DENTALES</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-14T09:00:00</t>
+          <t>2026-08-17T15:01:00</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5650,12 +5650,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5702,20 +5702,20 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>967490-14-LE26</t>
+          <t>1506668-9-LE26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MANT. Y REP. CANCHA DE ALTO RENDIMIENTO CABALLERÍA</t>
+          <t>MATERIAL DEPORTIVO Y MATERIAL MUSICAL</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-21T15:30:00</t>
+          <t>2026-08-03T17:30:00</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5783,20 +5783,20 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1389488-17-LP26</t>
+          <t>2157-78-LP26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUMINISTRO DE INDUMENTARIA ARTÍCULOS DEPORTIVOS   </t>
+          <t>CONVENIO DE MANTENIMIENTO PREVENTIVO Y CORRECTIVO PARA GRUPOS ELECTRÓGENOS FG WILSON 900KVA PERTENECIENTES AL HTC</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-06-04T16:37:00</t>
+          <t>2026-08-03T17:19:08.62</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5812,12 +5812,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5864,20 +5864,20 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1658-151-LP26</t>
+          <t>2183-9-LP26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>P.168-2026 OBRAS DE IMPERMEABILIZACIÓN DE GRADERÍAS TRIBUNA PACÍFICO ESTADIO MUNICIPAL GERMÁN BECKER TEMUCO</t>
+          <t>MANTENIMIENTO SEMESTRAL EQUIPOS DE CLIMATIZACIÓN</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-08-03T15:47:10.15</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5945,20 +5945,20 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2403-52-LP26</t>
+          <t>2261-21-O126</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Reposición calzada pasaje Maracaibo</t>
+          <t>Conservación camino Antiguo Angol Los Sauces, Región de La Araucanía</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-09-03T09:00:00</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6026,12 +6026,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4412-20-LP26</t>
+          <t>812799-44-LP26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO MULTICANCHAS EL RETIRO Y TUCUQUERE</t>
+          <t>REPOSICIÓN CENTRO COMUNITARIO 5 COMUNA DE MEJILLONES C.BIP 40074392-0</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-02T15:30:00</t>
+          <t>2026-08-31T15:00:00</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6107,20 +6107,20 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5908-25-LP26</t>
+          <t>821-8-O126</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>REPOSICIÓN ESCALERAS PÚBLICAS LOCALIDAD DE SIBAYA COMUNA DE HUARA</t>
+          <t>Reposición Cuartel BICRIM Ovalle</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-03T16:00:00</t>
+          <t>2026-08-03T08:26:23.16</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6188,20 +6188,20 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>812799-44-LP26</t>
+          <t>932-21-LE26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>REPOSICIÓN CENTRO COMUNITARIO 5 COMUNA DE MEJILLONES C.BIP 40074392-0</t>
+          <t>Mantenimiento preventivo y correctivo presurizador</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-31T15:00:00</t>
+          <t>2026-08-03T16:00:00</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6269,20 +6269,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>821-8-O126</t>
+          <t>3296-1-LE26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Reposición Cuartel BICRIM Ovalle</t>
+          <t>Contratación AITO conservación camino no enrolados 4 sectores rurales Curaco de Vélez.</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-08-03T08:26:23.16</t>
+          <t>2026-01-16T09:00:00</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -6350,20 +6350,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>932-21-LE26</t>
+          <t>1057472-87-LP26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Mantenimiento preventivo y correctivo presurizador</t>
+          <t>CONVENIO DE MANTENIMIENTO PARA LAVACHATAS MEIKO</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-03T16:00:00</t>
+          <t>2026-07-07T16:00:00</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6431,20 +6431,20 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3080-2-L126</t>
+          <t>1133353-35-LP26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE SERVICIO POR REPARACIÓN Y MANTENIMIENTO EDIFICIO MICALVI </t>
+          <t>CONVENIO DE SUMINISTRO DE MATERIALES DE CONSTRUCCIÓN PARA MANTENIMIENTO DE EDIFICIOS MUNICIPALES EMERGENCIA Y APOYO SOCIAL DE LA MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-13T17:30:00</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6512,20 +6512,20 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3436-86-L126</t>
+          <t>1198-24-LE26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mantenimiento de equipos de rancho Ítem 22.06.999 SIC 349184</t>
+          <t>Mantención y Obras Menores Estadio San Felipe</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-03T15:10:00</t>
+          <t>2026-08-13T15:00:00</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -6593,20 +6593,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3562-31-LR26</t>
+          <t>1199-11-LE26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN ESTADIO DE PUEBLO NUEVO LA CALERA</t>
+          <t>Mantener y Reparar Aire acondicionado IND MAULE</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-03T16:00:00</t>
+          <t>2026-08-03T17:00:00</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6674,20 +6674,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>359-91-LE26</t>
+          <t>1369-14-O126</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ADECUACIÓN DE RECINTOS PARA INSTALACIÓN DE TOMÓGRAFO COMPUTARIZADO EN EL INSTITUTO NACIONAL DEL CÁNCER</t>
+          <t xml:space="preserve">CONSERVACIÓN CAMINOS BÁSICOS B-383, CRUCE 23 CH, LAGUNA MISCANTI, PROV. EL </t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-08-03T16:00:00</t>
+          <t>2026-09-07T18:00:00</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6755,12 +6755,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3938-25-LE26</t>
+          <t>2430-61-LR26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mejoramiento Cierre Perimetral Recinto Deportivo Catripulli</t>
+          <t>“REPOSICIÓN Y MANTENCIÓN SISTEMA DE AUDIO DEL ESTADIO REGIONAL CALVO Y BASCUÑAN ANTOFAGASTA”</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-21T16:20:00</t>
+          <t>2026-09-17T11:00:00</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -6836,20 +6836,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3968-35-LE26</t>
+          <t>2704-57-LP26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>UNIFORMES DEPORTIVOS ESC. MONSEÑOR MANUEL LARRAIN</t>
+          <t>SC 3935 Servicio Mantenimiento prev y Correctivo de Calderas estufas de Tiro Balanceado termos</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-13T20:00:00</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -6865,12 +6865,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -6917,12 +6917,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4118-5-LP26</t>
+          <t>2792-9-L126</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ALUMBRADO PÚBLICO SECTOR COMUNA SANTA INÉS</t>
+          <t>REPOSICIÓN DE SILLÓN DENTAL PARA CESFAM LA PINCOYA</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-08-25T12:00:00</t>
+          <t>2026-08-13T09:00:00</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Certificación SEC (Chile)</t>
+          <t>Normativa estándar de licitación</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -6998,20 +6998,20 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2788-33-LP26</t>
+          <t>3416-45-L126</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>REPOSICIÓN MULTICANCHA VILLA LAS AMÉRICAS I PAINE</t>
+          <t xml:space="preserve">SERV. DE MANTENIMIENTO Y REPARACIÓN DE EQUIPOS </t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-08-03T15:01:00</t>
+          <t>2026-08-10T15:30:00</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -7079,20 +7079,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3565-54-LE26</t>
+          <t>3693-145-LE26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MATRERIALES PARA REPOSICION PASARELAS</t>
+          <t>ADQUISICIÓN DE VESTUARIO DEPORTIVO PARA ESTUDIANTE</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-08-14T12:24:00</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7108,12 +7108,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -7160,20 +7160,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>638-15-LE26</t>
+          <t>633-43-L126</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>REPARACIÓN MANTENIMIENTO Y NORMALIZACIÓN QUINCHO</t>
+          <t>CURSO DE CAPACITACIÓN EN PUEBLOS INDÍGENAS</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-07-20T15:30:00</t>
+          <t>2026-08-10T19:00:00</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -7241,20 +7241,20 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>898-42-R126</t>
+          <t>750998-47-LP26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO CENTRALES DE GASES CLINICOS</t>
+          <t>REPOSICIÓN CANCHA DE BABY FUTBOL CD LOS 56 UNIDOS</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-03-23T15:00:00</t>
+          <t>2026-08-03T15:15:00</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7270,12 +7270,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -7322,20 +7322,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4261-4-LE26</t>
+          <t>934-11-LE26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MTS Conservación CDI España Comuna de Angol</t>
+          <t>SERVICIO DE GUARDIAS IND REGION DE LOS LAGOS</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-08-03T16:20:14.27</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -7403,20 +7403,20 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>545598-24-LE26</t>
+          <t>935-17-LE26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE OXÍGENO MEDICINAL Y GASES CLÍNICOS CON CILINDROS EN ARRIENDO</t>
+          <t>INDUMENTARIA DEPORTIVA SNCD IND XII REGION</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-07-17T15:04:00</t>
+          <t>2026-08-14T09:00:00</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7484,12 +7484,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>584105-14-LP26</t>
+          <t>967490-14-LE26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>INCORPORACIÓN COMPONENTE INDÍGENA EN LA PLANIFICACIÓN ENERGÉTICA Y RESILIENCIA ENERGÉTICA EN RAPA NUI EN CUMPLIMIENTO CON EL PLAN SECTORIAL DE MITIGACIÓN Y DE ADAPTACIÓN AL CAMBIO CLIMÁTICO EN ENERGÍA</t>
+          <t>MANT. Y REP. CANCHA DE ALTO RENDIMIENTO CABALLERÍA</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-24T15:01:00</t>
+          <t>2026-08-21T15:30:00</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Certificación SEC (Chile)</t>
+          <t>Normativa estándar de licitación</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -7565,20 +7565,20 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>673663-15-LP26</t>
+          <t>3882-71-LE26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN RED ALUMBRADO PÚBLICO Y LUMINARIAS SO</t>
+          <t>REPOSICIÓN SISTEMA ELÉCTRICO CENTRAL DE CÁMARAS COMUNA DE LLAY LLAY</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-08-03T13:18:45.21</t>
+          <t>2026-08-17T15:00:00</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -7646,20 +7646,20 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>697057-29-LE26</t>
+          <t>407-101-LP26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Reposición cubierta de la Fiscalía de Pichilemu</t>
+          <t>MANTENIMIENTO PREVENTIVO Y REPARATIVO SIN REPUESTOS PARA ECÓGRAFOS</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-03T11:00:00</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -7727,20 +7727,20 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>618472-3-L126</t>
+          <t>4366-22-LP26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Servicio de mantenimiento, reparación y repuestos de Aire Acondicionado.</t>
+          <t>Rotura y reposición pavimento asfáltico</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-08-12T08:00:00</t>
+          <t>2026-08-03T15:04:02.44</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -7808,12 +7808,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>707426-25-LP26</t>
+          <t>4487-29-LE26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>REPOSICIÓN CUBIERTA Y SIST. ELECT. JI TIA NORA.</t>
+          <t>CONSERVACIÓN LICEO POLIVALENTE LA FRONTERA NEGRET</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-03T15:01:00</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -7889,20 +7889,20 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>740-12-LE26</t>
+          <t>5194-3-LE26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SERVICIO DE CATERING EN LA REGIÓN DEL MAULE INDAP</t>
+          <t>Adquisicion de Equipos Deportivos</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-08-31T16:30:00</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -7970,20 +7970,20 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>761391-107-L126</t>
+          <t>980313-25-LP26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DE/56/GUB/CURSO DE MANTENIMIENTO DE SISTEMAS DE REFRIGERACIÓN Y MANTENIMIENTO DE CALDERAS</t>
+          <t>CONSTRUCCIÓN CANCHA PASTO SINTÉTICO VILLA PELUCA</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-07-21T15:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -7999,12 +7999,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -8051,12 +8051,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>802-11-LE26</t>
+          <t>1798-5-LE26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Difusión y validación de un programa de Magíster en lengua y cultura indígena</t>
+          <t>Servicio de Mantenimiento de Red eléctrica y otros</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-06-23T10:00:00</t>
+          <t>2026-07-24T15:00:00</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -8132,20 +8132,20 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>826-11-O126</t>
+          <t>1951-31-LE26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>AIF OBRA REPOSICIÓN CONSULTORIO LAUTARO Y ADECUACIÓN A CESFAM</t>
+          <t>MANTENIMIENTO PREVENTIVO CORRECTIVO EQUIPOS REFRIG</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-08-19T09:00:00</t>
+          <t>2026-08-03T15:31:00</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8213,12 +8213,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1085111-21-LR26</t>
+          <t>2322-53-LR26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN MANT Y SEG PARQUE MONUM CHILLAN VIEJO</t>
+          <t xml:space="preserve">Construcción Cancha de Pasto Sintetico Meseta Azul  Vallenar </t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-08-03T16:00:00</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8242,12 +8242,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -8294,12 +8294,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1133353-34-LE26</t>
+          <t>2328-44-LE26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MECANICA DE SUELOS PROYECTO CONSTRUCCION POLIDEPORTIVO RAUCO</t>
+          <t>LICITACIÓN PÚBLICA E-472026 “ADQUISICION DE MATERIALES ELECTRICOS PARA LA ESPECIALIDAD DE ELECTRICIDAD TP 2024 LICEO INDUSTRIAL PUERTO MONTT”</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-03T15:03:00</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8375,20 +8375,20 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1232565-25-L126</t>
+          <t>2342-30-LP26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Adquisición de Equipamiento Deportivos Proyecto ULS 2595</t>
+          <t>MEJORAMIENTO MULTICANCHAS CASAS DEL PARQUE III LA PORTADA Y CONSTRUCCIÓN SANTA BÁRBARA SAN BERNARDO</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-10T17:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8456,20 +8456,20 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1263503-4-O126</t>
+          <t>3296-19-LE25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA IV</t>
+          <t>Contratación AITO conservación camino no enrolados 8 sectores rurales Curaco de Vélez.</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-08-03T11:07:24.06</t>
+          <t>2026-01-08T19:55:00</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -8537,20 +8537,20 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1434-21-LE26</t>
+          <t>4483-15-LR26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE EQUIPOS DENTALES</t>
+          <t>REPOSICION CUARTEL GENERAL 1° COMPAÑIA DE BOMBEROS TIERRA AMARILLA</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-08-17T15:01:00</t>
+          <t>2026-06-30T15:30:00</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -8618,20 +8618,20 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1506668-9-LE26</t>
+          <t>4494-47-LE26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MATERIAL DEPORTIVO Y MATERIAL MUSICAL</t>
+          <t>CONSERVACIÓN ESCUELA EDUARDO CAMPBELL PENCO</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-08-03T17:30:00</t>
+          <t>2026-08-18T15:00:00</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -8699,20 +8699,20 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2157-78-LP26</t>
+          <t>584264-35-LR26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CONVENIO DE MANTENIMIENTO PREVENTIVO Y CORRECTIVO PARA GRUPOS ELECTRÓGENOS FG WILSON 900KVA PERTENECIENTES AL HTC</t>
+          <t>SUM.SEÑALES DE TRANSITO DEMARCACIÓN INDEPENDENCIA</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-08-03T17:19:08.62</t>
+          <t>2026-09-04T15:05:00</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -8780,20 +8780,20 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2183-9-LP26</t>
+          <t>608897-45-LE26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO SEMESTRAL EQUIPOS DE CLIMATIZACIÓN</t>
+          <t>SISTEMATIZACIÓN DE INFORMACIÓN PARA LA IDENTIFICACIÓN DE PRIORIDADES DE CONSERVACIÓN MARINA PARA EL DISEÑO DE UNA RED DE ÁREAS MARINAS PROTEGIDAS EN LAS ECORREGIONES HUMBOLDTIANA CHILE CENTRAL ARAUCANA CHILOENSE Y CANALESFIORDOS DEL SUR DE CHILE</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-08-03T15:47:10.15</t>
+          <t>2026-08-13T16:00:00</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -8861,12 +8861,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2261-21-O126</t>
+          <t>610-13-LP26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Conservación camino Antiguo Angol Los Sauces, Región de La Araucanía</t>
+          <t>Determinación del Estándar Metodológico para el Cálculo de Rotura y Reposición de Pavimentos en Redes de Distribución</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-03T09:00:00</t>
+          <t>2026-08-21T15:00:00</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -8942,20 +8942,20 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2430-61-LR26</t>
+          <t>1481-5-L126</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>“REPOSICIÓN Y MANTENCIÓN SISTEMA DE AUDIO DEL ESTADIO REGIONAL CALVO Y BASCUÑAN ANTOFAGASTA”</t>
+          <t>COMPRA DE ARTICULOS DE LIBRERIA, MATERIAL PEDAGOGICO, DEPORTIVO, ALIMENTACION Y ASEO SAAT - INSTITUTO DE EDUCACION PARA EL ADULTO RBD 40008-4</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-17T11:00:00</t>
+          <t>2026-07-22T15:00:00</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9023,20 +9023,20 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2704-57-LP26</t>
+          <t>2467-79-LE26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SC 3935 Servicio Mantenimiento prev y Correctivo de Calderas estufas de Tiro Balanceado termos</t>
+          <t>ADQUISICIÓN DE CAMARAS DE SEGURIDAD PARA RECAMBIO</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-08-13T20:00:00</t>
+          <t>2026-08-03T15:20:00</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9104,20 +9104,20 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2792-9-L126</t>
+          <t>2760-100-LE26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>REPOSICIÓN DE SILLÓN DENTAL PARA CESFAM LA PINCOYA</t>
+          <t>PRODUCCION Y DESARROLLO DE EVENTOS JORNADA FAMILIAR INTERACTIVA DE LOS DERECHOS DE LAS NIÑAS Y NIÑOS 2026</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-08-13T09:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9178,27 +9178,27 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Plataforma Interact</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3416-45-L126</t>
+          <t>2793-104-LE26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERV. DE MANTENIMIENTO Y REPARACIÓN DE EQUIPOS </t>
+          <t>MANTENIMIENTO DE EQUIPOS Y SISTEMAS CLIMATIZACION</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-08-10T15:30:00</t>
+          <t>2026-08-03T15:01:00</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9266,20 +9266,20 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>3693-145-LE26</t>
+          <t>2981-204-LE26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE VESTUARIO DEPORTIVO PARA ESTUDIANTE</t>
+          <t>SERVICIO DE MANTENIMIENTO DE CALDERAS</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-08-14T15:00:00</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -9347,20 +9347,20 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3882-71-LE26</t>
+          <t>3084-15-R126</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>REPOSICIÓN SISTEMA ELÉCTRICO CENTRAL DE CÁMARAS COMUNA DE LLAY LLAY</t>
+          <t>“ADQUISICIÓN DE LICENCIAS OFFICE LTSC PRO PLUS 2024 LICENCIAS MICROSOFT WINDOWS 11 PRO LICENCIAS WINDOWS EXCHANGE SERVER 2019 LICENCIAS WINDOWS SERVER 2025 STANDARD 16 CORES ESP Y LICENCIAS EXCHANGE SERVER STANDARD 2019 CAL SU EQUIVALENTE TÉCNICO O SU</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-17T15:00:00</t>
+          <t>2026-06-03T15:00:00</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9376,12 +9376,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -9428,12 +9428,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>407-101-LP26</t>
+          <t>3621-39-LE26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO Y REPARATIVO SIN REPUESTOS PARA ECÓGRAFOS</t>
+          <t>INSTALACION DE ALUMBRADO PUBLICO ORNAMENTAL PASEO</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-08-03T16:20:00</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9509,20 +9509,20 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4366-22-LP26</t>
+          <t>3693-141-CO26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Rotura y reposición pavimento asfáltico</t>
+          <t>CONSERVACIÓN Y HABILITACIÓN SALAS DE BOMBAS COMPLEJO EDUCACIONAL CLARA SOLOVERA COLEGIO EL QUISCO Y ESCUELA POETA NERUDA</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-08-03T15:04:02.44</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -9590,20 +9590,20 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4487-29-LE26</t>
+          <t>407-86-LE26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN LICEO POLIVALENTE LA FRONTERA NEGRET</t>
+          <t>SERVICIO DE MANTENIMIENTO PREVENTIVO Y REPARATIVO SIN REPUESTOS PARA AUTOCLAVE</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-08-03T15:01:00</t>
+          <t>2026-08-03T10:53:14.54</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -9671,20 +9671,20 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>5194-3-LE26</t>
+          <t>638-15-LE26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Adquisicion de Equipos Deportivos</t>
+          <t>REPARACIÓN MANTENIMIENTO Y NORMALIZACIÓN QUINCHO</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-31T16:30:00</t>
+          <t>2026-07-20T15:30:00</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -9700,12 +9700,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -9752,20 +9752,20 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>980313-25-LP26</t>
+          <t>898-42-R126</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN CANCHA PASTO SINTÉTICO VILLA PELUCA</t>
+          <t>MANTENIMIENTO PREVENTIVO CENTRALES DE GASES CLINICOS</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-03-23T15:00:00</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">

--- a/agliluz/historial_licitaciones.xlsx
+++ b/agliluz/historial_licitaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q116"/>
+  <dimension ref="A1:T116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,6 +514,21 @@
           <t>Sistemas_Control_Telegestion</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Estado_Cumplimiento_Signify</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Analisis_Brecha_Tecnica</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Especificaciones_Signify_Match</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -577,22 +592,37 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
@@ -658,42 +688,57 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1057472-84-LP26</t>
+          <t>1186-2-LE26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CONVENIO DE MANTENIMIENTO PARA AUTOCLAVE STERRAD</t>
+          <t>SERVICIO DE MANTENIMIENTO DE ASCENSORES</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-07T16:00:00</t>
+          <t>2026-08-13T15:00:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -739,42 +784,57 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1150-14-O126</t>
+          <t>1225288-2-LE26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Conservación Cauces Naturales Rio Clarillo 2026</t>
+          <t>IMPLEMENTACIÓN TALLERES DEPORTIVOS RECREATIVOS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-06-26T16:30:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -790,12 +850,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,42 +880,57 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211839-53-LE26</t>
+          <t>1263503-1-O126</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE MATERIALES E IMPLEMENTOS DEPORTIVOS</t>
+          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA I</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-03T10:51:48.64</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -871,12 +946,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -901,34 +976,49 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2186-21-LE26</t>
+          <t>1306643-23-LE26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO PARA CALDERAS</t>
+          <t>SERVICIO DE REPOSICIÓN MAMPARAS CESFAM</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -936,7 +1026,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-18T12:00:00</t>
+          <t>2026-08-18T15:00:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -982,42 +1072,57 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1263503-2-O126</t>
+          <t>2186-21-LE26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA II</t>
+          <t>MANTENIMIENTO PREVENTIVO PARA CALDERAS</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-03T11:03:43.517</t>
+          <t>2026-08-18T12:00:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1063,34 +1168,49 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1216085-36-LE26</t>
+          <t>1057472-84-LP26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO ASCENSORES</t>
+          <t>CONVENIO DE MANTENIMIENTO PARA AUTOCLAVE STERRAD</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1098,7 +1218,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-26T15:30:00</t>
+          <t>2026-07-07T16:00:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1144,42 +1264,57 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1537592-4-LE26</t>
+          <t>1150-14-O126</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Adquisición de Herramientas Instrumentos y Equipos Especializados para Mantenimiento Industrial</t>
+          <t>Conservación Cauces Naturales Rio Clarillo 2026</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-13T16:17:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1195,12 +1330,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1225,42 +1360,57 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1537592-5-LE26</t>
+          <t>1211839-53-LE26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Adquisición de insumos de ferretería pintura limpieza y mantenimiento - LBV</t>
+          <t>ADQUISICIÓN DE MATERIALES E IMPLEMENTOS DEPORTIVOS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-13T18:48:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1276,12 +1426,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1306,34 +1456,49 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1048-55-LE26</t>
+          <t>2274-30-LE26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ADQ. VESTUARIO Y EPP PERSONAL LUMINARIA 2do LLAMAD</t>
+          <t>PROPUESTA PUBLICA ADQUISICION MATERIAL DE ENSEÑANZA E INSUMOS DEPORTIVOS CONVENIO LA PINTANA 2026 EXP. 11856</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1341,7 +1506,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-03T18:40:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1357,12 +1522,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1387,34 +1552,49 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1063538-165-LP26</t>
+          <t>2328-46-LE26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CONVENIO MANTENIMIENTO DE EQUIPOS MEDICOS</t>
+          <t>LICITACIÓN PÚBLICA E-55 ADQUISICION DE CALZADO DEPORTIVO JARDINES INFANTILES DEPENDIENTES DEL DAEM DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1422,7 +1602,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-03T16:15:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1438,12 +1618,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1468,42 +1648,57 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1063538-185-LP26</t>
+          <t>2332-78-L126</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO SISTEMA GASES CLINICOS</t>
+          <t>SERVICIOS DE CONSERVACIÓN DE INFRAESTRUCTURA DEL SAR ALERCE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-14T15:15:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1549,42 +1744,57 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1344402-6-E226</t>
+          <t>2345-127-LE26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MANTENCIÓN Y DIAGNÓSTICO CÁMARAS DE CONSERVACIÓN</t>
+          <t>ADQUISICIÓN DE ARTÍCULOS DEPORTIVOS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-08-17T15:01:00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1600,12 +1810,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1630,42 +1840,57 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2332-78-L126</t>
+          <t>2765-44-E226</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SERVICIOS DE CONSERVACIÓN DE INFRAESTRUCTURA DEL SAR ALERCE</t>
+          <t>SERVICIO DE MANTENIMIENTO CENTRO COMUNITARIO SERGI</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-10T16:23:00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1711,42 +1936,57 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2345-127-LE26</t>
+          <t>3390-21-LE26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ARTÍCULOS DEPORTIVOS</t>
+          <t>Materiales para Mantenimiento y Reparaciones.</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-17T15:01:00</t>
+          <t>2026-08-03T15:57:00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1762,12 +2002,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1792,34 +2032,49 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2765-44-E226</t>
+          <t>3562-28-LR26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO CENTRO COMUNITARIO SERGI</t>
+          <t>CONSERVACIÓN COMPLEJO DEPORTIVO ESPERANZA CALERA</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1827,7 +2082,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-10T16:23:00</t>
+          <t>2026-09-03T16:37:00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1843,12 +2098,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1873,34 +2128,49 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3390-21-LE26</t>
+          <t>1048-55-LE26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Materiales para Mantenimiento y Reparaciones.</t>
+          <t>ADQ. VESTUARIO Y EPP PERSONAL LUMINARIA 2do LLAMAD</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1908,7 +2178,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-03T15:57:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1954,42 +2224,57 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3562-28-LR26</t>
+          <t>1063538-165-LP26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN COMPLEJO DEPORTIVO ESPERANZA CALERA</t>
+          <t>CONVENIO MANTENIMIENTO DE EQUIPOS MEDICOS</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-03T16:37:00</t>
+          <t>2026-08-03T16:15:00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2005,12 +2290,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2035,42 +2320,57 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1389488-17-LP26</t>
+          <t>1063538-185-LP26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUMINISTRO DE INDUMENTARIA ARTÍCULOS DEPORTIVOS   </t>
+          <t>MANTENIMIENTO SISTEMA GASES CLINICOS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-04T16:37:00</t>
+          <t>2026-08-14T15:15:00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2086,12 +2386,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2116,34 +2416,49 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1658-151-LP26</t>
+          <t>1344402-6-E226</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>P.168-2026 OBRAS DE IMPERMEABILIZACIÓN DE GRADERÍAS TRIBUNA PACÍFICO ESTADIO MUNICIPAL GERMÁN BECKER TEMUCO</t>
+          <t>MANTENCIÓN Y DIAGNÓSTICO CÁMARAS DE CONSERVACIÓN</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2167,12 +2482,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2197,42 +2512,57 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2403-52-LP26</t>
+          <t>1216085-36-LE26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Reposición calzada pasaje Maracaibo</t>
+          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO ASCENSORES</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-06-26T15:30:00</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2278,34 +2608,49 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2744-26-L126</t>
+          <t>1537592-4-LE26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO INTEGRAL DE AUTOCLAVE</t>
+          <t>Adquisición de Herramientas Instrumentos y Equipos Especializados para Mantenimiento Industrial</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2313,7 +2658,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-10T15:47:00</t>
+          <t>2026-08-13T16:17:00</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2329,12 +2674,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2359,42 +2704,57 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3326-35-LE26</t>
+          <t>1537592-5-LE26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN E INSTALACIÓN DE ACCESORIO PARA EL VEHÍCULO FISCAL AC-2429 MARCA NISSAN MODELO PATHFINDER AÑO 2026 DE CARGO DE LA SUBDIRECCIÓN GENERAL SEGÚN BASES ADMINISTRATIVAS Y TÉCNICAS</t>
+          <t>Adquisición de insumos de ferretería pintura limpieza y mantenimiento - LBV</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-03T18:03:05.86</t>
+          <t>2026-08-13T18:48:00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2410,12 +2770,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2440,42 +2800,57 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2328-43-LE26</t>
+          <t>1057472-87-LP26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA E-502026  “ADQUISICION DE EQUIPAMIENTO PARA LA ESPECIALIDAD DE MECANICA INDUSTRIAL DEL LICEO INDUSTRIAL PUERTO MONTT FONDO TP 2024”</t>
+          <t>CONVENIO DE MANTENIMIENTO PARA LAVACHATAS MEIKO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-03T15:52:00</t>
+          <t>2026-07-07T16:00:00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2491,12 +2866,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2521,34 +2896,49 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1186-2-LE26</t>
+          <t>1133353-35-LP26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO DE ASCENSORES</t>
+          <t>CONVENIO DE SUMINISTRO DE MATERIALES DE CONSTRUCCIÓN PARA MANTENIMIENTO DE EDIFICIOS MUNICIPALES EMERGENCIA Y APOYO SOCIAL DE LA MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2556,7 +2946,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-13T15:00:00</t>
+          <t>2026-08-13T17:30:00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2602,42 +2992,57 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1225288-2-LE26</t>
+          <t>1198-24-LE26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IMPLEMENTACIÓN TALLERES DEPORTIVOS RECREATIVOS</t>
+          <t>Mantención y Obras Menores Estadio San Felipe</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-26T16:30:00</t>
+          <t>2026-08-13T15:00:00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2683,42 +3088,57 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1263503-1-O126</t>
+          <t>1199-11-LE26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA I</t>
+          <t>Mantener y Reparar Aire acondicionado IND MAULE</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-03T10:51:48.64</t>
+          <t>2026-08-03T17:00:00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2734,12 +3154,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2764,34 +3184,49 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1306643-23-LE26</t>
+          <t>1369-14-O126</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SERVICIO DE REPOSICIÓN MAMPARAS CESFAM</t>
+          <t xml:space="preserve">CONSERVACIÓN CAMINOS BÁSICOS B-383, CRUCE 23 CH, LAGUNA MISCANTI, PROV. EL </t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2799,7 +3234,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-08-18T15:00:00</t>
+          <t>2026-09-07T18:00:00</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2845,42 +3280,57 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2788-33-LP26</t>
+          <t>3296-1-LE26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>REPOSICIÓN MULTICANCHA VILLA LAS AMÉRICAS I PAINE</t>
+          <t>Contratación AITO conservación camino no enrolados 4 sectores rurales Curaco de Vélez.</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-08-03T15:01:00</t>
+          <t>2026-01-16T09:00:00</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2896,12 +3346,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2926,34 +3376,49 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3565-54-LE26</t>
+          <t>4412-20-LP26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MATRERIALES PARA REPOSICION PASARELAS</t>
+          <t>MEJORAMIENTO MULTICANCHAS EL RETIRO Y TUCUQUERE</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2961,7 +3426,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-08-14T12:24:00</t>
+          <t>2026-09-02T15:30:00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2977,12 +3442,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3007,42 +3472,57 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4412-20-LP26</t>
+          <t>5908-25-LP26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO MULTICANCHAS EL RETIRO Y TUCUQUERE</t>
+          <t>REPOSICIÓN ESCALERAS PÚBLICAS LOCALIDAD DE SIBAYA COMUNA DE HUARA</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-02T15:30:00</t>
+          <t>2026-08-03T16:00:00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3058,12 +3538,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3088,42 +3568,57 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5908-25-LP26</t>
+          <t>1263503-2-O126</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>REPOSICIÓN ESCALERAS PÚBLICAS LOCALIDAD DE SIBAYA COMUNA DE HUARA</t>
+          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA II</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-08-03T16:00:00</t>
+          <t>2026-08-03T11:03:43.517</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3169,42 +3664,57 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3399-17-L126</t>
+          <t>2328-43-LE26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Servicio de mantenimiento para el mini bus Merces Benz Sprinter del Regimiento N° 16 Talca.</t>
+          <t>LICITACIÓN PÚBLICA E-502026  “ADQUISICION DE EQUIPAMIENTO PARA LA ESPECIALIDAD DE MECANICA INDUSTRIAL DEL LICEO INDUSTRIAL PUERTO MONTT FONDO TP 2024”</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-30T15:56:00</t>
+          <t>2026-08-03T15:52:00</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3220,12 +3730,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3250,34 +3760,49 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3482-6-LE26</t>
+          <t>2744-26-L126</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mantenimiento y Reparación de Baño.</t>
+          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO INTEGRAL DE AUTOCLAVE</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3285,7 +3810,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-08-10T16:00:00</t>
+          <t>2026-08-10T15:47:00</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3331,42 +3856,57 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1057472-85-LP26</t>
+          <t>3326-35-LE26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CONVENIO MANTENIMIENTO EQUIPOS Y TORRES ENDOSCOPIA</t>
+          <t>ADQUISICIÓN E INSTALACIÓN DE ACCESORIO PARA EL VEHÍCULO FISCAL AC-2429 MARCA NISSAN MODELO PATHFINDER AÑO 2026 DE CARGO DE LA SUBDIRECCIÓN GENERAL SEGÚN BASES ADMINISTRATIVAS Y TÉCNICAS</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-07-07T16:00:00</t>
+          <t>2026-08-03T18:03:05.86</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3382,12 +3922,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3412,34 +3952,49 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1225288-5-LE26</t>
+          <t>1481-5-L126</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IMPLEMENTACIÓN PARA APOYO CLUBES DEPORTIVOS</t>
+          <t>COMPRA DE ARTICULOS DE LIBRERIA, MATERIAL PEDAGOGICO, DEPORTIVO, ALIMENTACION Y ASEO SAAT - INSTITUTO DE EDUCACION PARA EL ADULTO RBD 40008-4</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3447,7 +4002,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-26T16:30:00</t>
+          <t>2026-07-22T15:00:00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3493,34 +4048,49 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1233616-49-LE26</t>
+          <t>2467-79-LE26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO IMPRESORAS Y MULTIFUNCIONALES EE.EE</t>
+          <t>ADQUISICIÓN DE CAMARAS DE SEGURIDAD PARA RECAMBIO</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3528,7 +4098,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-03T15:20:00</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3574,42 +4144,57 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1233616-51-L126</t>
+          <t>1085111-21-LR26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO TORRES DE COMUNICACIÓN ARRIOSTRADA</t>
+          <t>CONSERVACIÓN MANT Y SEG PARQUE MONUM CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-03T15:04:02.473</t>
+          <t>2026-08-03T16:00:00</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3655,34 +4240,49 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1085111-21-LR26</t>
+          <t>1133353-34-LE26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN MANT Y SEG PARQUE MONUM CHILLAN VIEJO</t>
+          <t>MECANICA DE SUELOS PROYECTO CONSTRUCCION POLIDEPORTIVO RAUCO</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3690,7 +4290,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-08-03T16:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3706,12 +4306,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3736,42 +4336,57 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1133353-34-LE26</t>
+          <t>1232565-25-L126</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MECANICA DE SUELOS PROYECTO CONSTRUCCION POLIDEPORTIVO RAUCO</t>
+          <t>Adquisición de Equipamiento Deportivos Proyecto ULS 2595</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-10T17:00:00</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3817,42 +4432,57 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1232565-25-L126</t>
+          <t>1263503-4-O126</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Adquisición de Equipamiento Deportivos Proyecto ULS 2595</t>
+          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA IV</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-10T17:00:00</t>
+          <t>2026-08-03T11:07:24.06</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3868,12 +4498,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3898,42 +4528,57 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1263503-4-O126</t>
+          <t>1057472-85-LP26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA IV</t>
+          <t>CONVENIO MANTENIMIENTO EQUIPOS Y TORRES ENDOSCOPIA</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-03T11:07:24.06</t>
+          <t>2026-07-07T16:00:00</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3979,42 +4624,57 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3080-2-L126</t>
+          <t>1225288-5-LE26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE SERVICIO POR REPARACIÓN Y MANTENIMIENTO EDIFICIO MICALVI </t>
+          <t>IMPLEMENTACIÓN PARA APOYO CLUBES DEPORTIVOS</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-06-26T16:30:00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4030,12 +4690,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4060,34 +4720,49 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3436-86-L126</t>
+          <t>1233616-49-LE26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mantenimiento de equipos de rancho Ítem 22.06.999 SIC 349184</t>
+          <t>MANTENIMIENTO IMPRESORAS Y MULTIFUNCIONALES EE.EE</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4095,7 +4770,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-03T15:10:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4141,42 +4816,57 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3562-31-LR26</t>
+          <t>1233616-51-L126</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN ESTADIO DE PUEBLO NUEVO LA CALERA</t>
+          <t>MANTENIMIENTO TORRES DE COMUNICACIÓN ARRIOSTRADA</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-03T16:00:00</t>
+          <t>2026-08-03T15:04:02.473</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4192,12 +4882,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4222,42 +4912,57 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>359-91-LE26</t>
+          <t>633-43-L126</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ADECUACIÓN DE RECINTOS PARA INSTALACIÓN DE TOMÓGRAFO COMPUTARIZADO EN EL INSTITUTO NACIONAL DEL CÁNCER</t>
+          <t>CURSO DE CAPACITACIÓN EN PUEBLOS INDÍGENAS</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-08-03T16:00:00</t>
+          <t>2026-08-10T19:00:00</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4273,12 +4978,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4303,42 +5008,57 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3938-25-LE26</t>
+          <t>750998-47-LP26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mejoramiento Cierre Perimetral Recinto Deportivo Catripulli</t>
+          <t>REPOSICIÓN CANCHA DE BABY FUTBOL CD LOS 56 UNIDOS</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-21T16:20:00</t>
+          <t>2026-08-03T15:15:00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4384,34 +5104,49 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3968-35-LE26</t>
+          <t>934-11-LE26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>UNIFORMES DEPORTIVOS ESC. MONSEÑOR MANUEL LARRAIN</t>
+          <t>SERVICIO DE GUARDIAS IND REGION DE LOS LAGOS</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4465,34 +5200,49 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4118-5-LP26</t>
+          <t>935-17-LE26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ALUMBRADO PÚBLICO SECTOR COMUNA SANTA INÉS</t>
+          <t>INDUMENTARIA DEPORTIVA SNCD IND XII REGION</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -4500,7 +5250,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-25T12:00:00</t>
+          <t>2026-08-14T09:00:00</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4516,12 +5266,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4546,34 +5296,49 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Certificación SEC (Chile)</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>618472-3-L126</t>
+          <t>967490-14-LE26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Servicio de mantenimiento, reparación y repuestos de Aire Acondicionado.</t>
+          <t>MANT. Y REP. CANCHA DE ALTO RENDIMIENTO CABALLERÍA</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -4581,7 +5346,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-12T08:00:00</t>
+          <t>2026-08-21T15:30:00</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4597,12 +5362,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4627,34 +5392,49 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>707426-25-LP26</t>
+          <t>3080-2-L126</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>REPOSICIÓN CUBIERTA Y SIST. ELECT. JI TIA NORA.</t>
+          <t xml:space="preserve">ADQUISICIÓN DE SERVICIO POR REPARACIÓN Y MANTENIMIENTO EDIFICIO MICALVI </t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -4708,34 +5488,49 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>740-12-LE26</t>
+          <t>3436-86-L126</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SERVICIO DE CATERING EN LA REGIÓN DEL MAULE INDAP</t>
+          <t>Mantenimiento de equipos de rancho Ítem 22.06.999 SIC 349184</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4743,7 +5538,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-08-03T15:10:00</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4759,12 +5554,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4789,42 +5584,57 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>761391-107-L126</t>
+          <t>3562-31-LR26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DE/56/GUB/CURSO DE MANTENIMIENTO DE SISTEMAS DE REFRIGERACIÓN Y MANTENIMIENTO DE CALDERAS</t>
+          <t>CONSERVACIÓN ESTADIO DE PUEBLO NUEVO LA CALERA</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-21T15:00:00</t>
+          <t>2026-09-03T16:00:00</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4840,12 +5650,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4870,42 +5680,57 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>802-11-LE26</t>
+          <t>359-91-LE26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Difusión y validación de un programa de Magíster en lengua y cultura indígena</t>
+          <t>ADECUACIÓN DE RECINTOS PARA INSTALACIÓN DE TOMÓGRAFO COMPUTARIZADO EN EL INSTITUTO NACIONAL DEL CÁNCER</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-23T10:00:00</t>
+          <t>2026-08-03T16:00:00</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4921,12 +5746,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4951,34 +5776,49 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>826-11-O126</t>
+          <t>3938-25-LE26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AIF OBRA REPOSICIÓN CONSULTORIO LAUTARO Y ADECUACIÓN A CESFAM</t>
+          <t>Mejoramiento Cierre Perimetral Recinto Deportivo Catripulli</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -4986,7 +5826,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-19T09:00:00</t>
+          <t>2026-08-21T16:20:00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5002,12 +5842,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5032,34 +5872,49 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2274-30-LE26</t>
+          <t>3968-35-LE26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PROPUESTA PUBLICA ADQUISICION MATERIAL DE ENSEÑANZA E INSUMOS DEPORTIVOS CONVENIO LA PINTANA 2026 EXP. 11856</t>
+          <t>UNIFORMES DEPORTIVOS ESC. MONSEÑOR MANUEL LARRAIN</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -5067,7 +5922,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-03T18:40:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5113,42 +5968,57 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2328-46-LE26</t>
+          <t>4118-5-LP26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA E-55 ADQUISICION DE CALZADO DEPORTIVO JARDINES INFANTILES DEPENDIENTES DEL DAEM DE PUERTO MONTT</t>
+          <t>ALUMBRADO PÚBLICO SECTOR COMUNA SANTA INÉS</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-25T12:00:00</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5164,12 +6034,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5194,42 +6064,57 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4261-4-LE26</t>
+          <t>812799-44-LP26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MTS Conservación CDI España Comuna de Angol</t>
+          <t>REPOSICIÓN CENTRO COMUNITARIO 5 COMUNA DE MEJILLONES C.BIP 40074392-0</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-03T16:20:14.27</t>
+          <t>2026-08-31T15:00:00</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5275,42 +6160,57 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>545598-24-LE26</t>
+          <t>821-8-O126</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE OXÍGENO MEDICINAL Y GASES CLÍNICOS CON CILINDROS EN ARRIENDO</t>
+          <t>Reposición Cuartel BICRIM Ovalle</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-07-17T15:04:00</t>
+          <t>2026-08-03T08:26:23.16</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5326,12 +6226,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5356,42 +6256,57 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>584105-14-LP26</t>
+          <t>932-21-LE26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>INCORPORACIÓN COMPONENTE INDÍGENA EN LA PLANIFICACIÓN ENERGÉTICA Y RESILIENCIA ENERGÉTICA EN RAPA NUI EN CUMPLIMIENTO CON EL PLAN SECTORIAL DE MITIGACIÓN Y DE ADAPTACIÓN AL CAMBIO CLIMÁTICO EN ENERGÍA</t>
+          <t>Mantenimiento preventivo y correctivo presurizador</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-24T15:01:00</t>
+          <t>2026-08-03T16:00:00</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5407,12 +6322,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5437,42 +6352,57 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Certificación SEC (Chile)</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>673663-15-LP26</t>
+          <t>618472-3-L126</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN RED ALUMBRADO PÚBLICO Y LUMINARIAS SO</t>
+          <t>Servicio de mantenimiento, reparación y repuestos de Aire Acondicionado.</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-03T13:18:45.21</t>
+          <t>2026-08-12T08:00:00</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5518,42 +6448,57 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>697057-29-LE26</t>
+          <t>707426-25-LP26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Reposición cubierta de la Fiscalía de Pichilemu</t>
+          <t>REPOSICIÓN CUBIERTA Y SIST. ELECT. JI TIA NORA.</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-03T11:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5599,42 +6544,57 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1434-21-LE26</t>
+          <t>740-12-LE26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE EQUIPOS DENTALES</t>
+          <t>SERVICIO DE CATERING EN LA REGIÓN DEL MAULE INDAP</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-17T15:01:00</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5650,12 +6610,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5680,42 +6640,57 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1506668-9-LE26</t>
+          <t>761391-107-L126</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MATERIAL DEPORTIVO Y MATERIAL MUSICAL</t>
+          <t>DE/56/GUB/CURSO DE MANTENIMIENTO DE SISTEMAS DE REFRIGERACIÓN Y MANTENIMIENTO DE CALDERAS</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-03T17:30:00</t>
+          <t>2026-07-21T15:00:00</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5731,12 +6706,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5761,42 +6736,57 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2157-78-LP26</t>
+          <t>802-11-LE26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CONVENIO DE MANTENIMIENTO PREVENTIVO Y CORRECTIVO PARA GRUPOS ELECTRÓGENOS FG WILSON 900KVA PERTENECIENTES AL HTC</t>
+          <t>Difusión y validación de un programa de Magíster en lengua y cultura indígena</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-08-03T17:19:08.62</t>
+          <t>2026-06-23T10:00:00</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5812,12 +6802,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5842,42 +6832,57 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2183-9-LP26</t>
+          <t>826-11-O126</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO SEMESTRAL EQUIPOS DE CLIMATIZACIÓN</t>
+          <t>AIF OBRA REPOSICIÓN CONSULTORIO LAUTARO Y ADECUACIÓN A CESFAM</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-03T15:47:10.15</t>
+          <t>2026-08-19T09:00:00</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5923,42 +6928,57 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2261-21-O126</t>
+          <t>1389488-17-LP26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Conservación camino Antiguo Angol Los Sauces, Región de La Araucanía</t>
+          <t xml:space="preserve">SUMINISTRO DE INDUMENTARIA ARTÍCULOS DEPORTIVOS   </t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-03T09:00:00</t>
+          <t>2026-06-04T16:37:00</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5974,12 +6994,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6004,42 +7024,57 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>812799-44-LP26</t>
+          <t>1658-151-LP26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>REPOSICIÓN CENTRO COMUNITARIO 5 COMUNA DE MEJILLONES C.BIP 40074392-0</t>
+          <t>P.168-2026 OBRAS DE IMPERMEABILIZACIÓN DE GRADERÍAS TRIBUNA PACÍFICO ESTADIO MUNICIPAL GERMÁN BECKER TEMUCO</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-08-31T15:00:00</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6055,12 +7090,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6085,42 +7120,57 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>821-8-O126</t>
+          <t>2403-52-LP26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Reposición Cuartel BICRIM Ovalle</t>
+          <t>Reposición calzada pasaje Maracaibo</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-03T08:26:23.16</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6166,42 +7216,57 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>932-21-LE26</t>
+          <t>1434-21-LE26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Mantenimiento preventivo y correctivo presurizador</t>
+          <t>MANTENIMIENTO DE EQUIPOS DENTALES</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-03T16:00:00</t>
+          <t>2026-08-17T15:01:00</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6247,42 +7312,57 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3296-1-LE26</t>
+          <t>1506668-9-LE26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Contratación AITO conservación camino no enrolados 4 sectores rurales Curaco de Vélez.</t>
+          <t>MATERIAL DEPORTIVO Y MATERIAL MUSICAL</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-01-16T09:00:00</t>
+          <t>2026-08-03T17:30:00</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6298,12 +7378,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6328,42 +7408,57 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Certificación SEC (Chile)</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1057472-87-LP26</t>
+          <t>2157-78-LP26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CONVENIO DE MANTENIMIENTO PARA LAVACHATAS MEIKO</t>
+          <t>CONVENIO DE MANTENIMIENTO PREVENTIVO Y CORRECTIVO PARA GRUPOS ELECTRÓGENOS FG WILSON 900KVA PERTENECIENTES AL HTC</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-07-07T16:00:00</t>
+          <t>2026-08-03T17:19:08.62</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6409,42 +7504,57 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1133353-35-LP26</t>
+          <t>2183-9-LP26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE MATERIALES DE CONSTRUCCIÓN PARA MANTENIMIENTO DE EDIFICIOS MUNICIPALES EMERGENCIA Y APOYO SOCIAL DE LA MUNICIPALIDAD DE RAUCO</t>
+          <t>MANTENIMIENTO SEMESTRAL EQUIPOS DE CLIMATIZACIÓN</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-13T17:30:00</t>
+          <t>2026-08-03T15:47:10.15</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6490,34 +7600,49 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1198-24-LE26</t>
+          <t>2261-21-O126</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mantención y Obras Menores Estadio San Felipe</t>
+          <t>Conservación camino Antiguo Angol Los Sauces, Región de La Araucanía</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -6525,7 +7650,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-13T15:00:00</t>
+          <t>2026-09-03T09:00:00</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6541,12 +7666,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -6571,42 +7696,57 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1199-11-LE26</t>
+          <t>3399-17-L126</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Mantener y Reparar Aire acondicionado IND MAULE</t>
+          <t>Servicio de mantenimiento para el mini bus Merces Benz Sprinter del Regimiento N° 16 Talca.</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-08-03T17:00:00</t>
+          <t>2026-07-30T15:56:00</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6622,12 +7762,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -6652,34 +7792,49 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1369-14-O126</t>
+          <t>3482-6-LE26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONSERVACIÓN CAMINOS BÁSICOS B-383, CRUCE 23 CH, LAGUNA MISCANTI, PROV. EL </t>
+          <t>Mantenimiento y Reparación de Baño.</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -6687,7 +7842,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-07T18:00:00</t>
+          <t>2026-08-10T16:00:00</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6733,22 +7888,37 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
@@ -6814,22 +7984,37 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
@@ -6895,22 +8080,37 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
@@ -6976,22 +8176,37 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
@@ -7057,22 +8272,37 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
@@ -7138,42 +8368,57 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>633-43-L126</t>
+          <t>2788-33-LP26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CURSO DE CAPACITACIÓN EN PUEBLOS INDÍGENAS</t>
+          <t>REPOSICIÓN MULTICANCHA VILLA LAS AMÉRICAS I PAINE</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-08-10T19:00:00</t>
+          <t>2026-08-03T15:01:00</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7219,42 +8464,57 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>750998-47-LP26</t>
+          <t>3565-54-LE26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>REPOSICIÓN CANCHA DE BABY FUTBOL CD LOS 56 UNIDOS</t>
+          <t>MATRERIALES PARA REPOSICION PASARELAS</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-08-03T15:15:00</t>
+          <t>2026-08-14T12:24:00</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7270,12 +8530,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -7300,42 +8560,57 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>934-11-LE26</t>
+          <t>4261-4-LE26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SERVICIO DE GUARDIAS IND REGION DE LOS LAGOS</t>
+          <t>MTS Conservación CDI España Comuna de Angol</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-03T16:20:14.27</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7351,12 +8626,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -7381,42 +8656,57 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>935-17-LE26</t>
+          <t>545598-24-LE26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>INDUMENTARIA DEPORTIVA SNCD IND XII REGION</t>
+          <t>CONVENIO DE SUMINISTRO DE OXÍGENO MEDICINAL Y GASES CLÍNICOS CON CILINDROS EN ARRIENDO</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-08-14T09:00:00</t>
+          <t>2026-07-17T15:04:00</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7462,34 +8752,49 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>967490-14-LE26</t>
+          <t>584105-14-LP26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MANT. Y REP. CANCHA DE ALTO RENDIMIENTO CABALLERÍA</t>
+          <t>INCORPORACIÓN COMPONENTE INDÍGENA EN LA PLANIFICACIÓN ENERGÉTICA Y RESILIENCIA ENERGÉTICA EN RAPA NUI EN CUMPLIMIENTO CON EL PLAN SECTORIAL DE MITIGACIÓN Y DE ADAPTACIÓN AL CAMBIO CLIMÁTICO EN ENERGÍA</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -7497,7 +8802,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-21T15:30:00</t>
+          <t>2026-08-24T15:01:00</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7543,42 +8848,57 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3882-71-LE26</t>
+          <t>673663-15-LP26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>REPOSICIÓN SISTEMA ELÉCTRICO CENTRAL DE CÁMARAS COMUNA DE LLAY LLAY</t>
+          <t>CONSTRUCCIÓN RED ALUMBRADO PÚBLICO Y LUMINARIAS SO</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-08-17T15:00:00</t>
+          <t>2026-08-03T13:18:45.21</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -7624,42 +8944,57 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>407-101-LP26</t>
+          <t>697057-29-LE26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO Y REPARATIVO SIN REPUESTOS PARA ECÓGRAFOS</t>
+          <t>Reposición cubierta de la Fiscalía de Pichilemu</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-09-03T11:00:00</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -7705,42 +9040,57 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4366-22-LP26</t>
+          <t>1798-5-LE26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Rotura y reposición pavimento asfáltico</t>
+          <t>Servicio de Mantenimiento de Red eléctrica y otros</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-08-03T15:04:02.44</t>
+          <t>2026-07-24T15:00:00</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -7786,34 +9136,49 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4487-29-LE26</t>
+          <t>1951-31-LE26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN LICEO POLIVALENTE LA FRONTERA NEGRET</t>
+          <t>MANTENIMIENTO PREVENTIVO CORRECTIVO EQUIPOS REFRIG</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -7821,7 +9186,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-08-03T15:01:00</t>
+          <t>2026-08-03T15:31:00</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -7867,42 +9232,57 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5194-3-LE26</t>
+          <t>2322-53-LR26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Adquisicion de Equipos Deportivos</t>
+          <t xml:space="preserve">Construcción Cancha de Pasto Sintetico Meseta Azul  Vallenar </t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-08-31T16:30:00</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -7948,34 +9328,49 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>980313-25-LP26</t>
+          <t>2328-44-LE26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN CANCHA PASTO SINTÉTICO VILLA PELUCA</t>
+          <t>LICITACIÓN PÚBLICA E-472026 “ADQUISICION DE MATERIALES ELECTRICOS PARA LA ESPECIALIDAD DE ELECTRICIDAD TP 2024 LICEO INDUSTRIAL PUERTO MONTT”</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -7983,7 +9378,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-03T15:03:00</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8029,42 +9424,57 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1798-5-LE26</t>
+          <t>2342-30-LP26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Servicio de Mantenimiento de Red eléctrica y otros</t>
+          <t>MEJORAMIENTO MULTICANCHAS CASAS DEL PARQUE III LA PORTADA Y CONSTRUCCIÓN SANTA BÁRBARA SAN BERNARDO</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-07-24T15:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8080,12 +9490,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -8110,42 +9520,57 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1951-31-LE26</t>
+          <t>3882-71-LE26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO CORRECTIVO EQUIPOS REFRIG</t>
+          <t>REPOSICIÓN SISTEMA ELÉCTRICO CENTRAL DE CÁMARAS COMUNA DE LLAY LLAY</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-08-03T15:31:00</t>
+          <t>2026-08-17T15:00:00</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8191,34 +9616,49 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2322-53-LR26</t>
+          <t>407-101-LP26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construcción Cancha de Pasto Sintetico Meseta Azul  Vallenar </t>
+          <t>MANTENIMIENTO PREVENTIVO Y REPARATIVO SIN REPUESTOS PARA ECÓGRAFOS</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -8242,12 +9682,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -8272,42 +9712,57 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2328-44-LE26</t>
+          <t>4366-22-LP26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA E-472026 “ADQUISICION DE MATERIALES ELECTRICOS PARA LA ESPECIALIDAD DE ELECTRICIDAD TP 2024 LICEO INDUSTRIAL PUERTO MONTT”</t>
+          <t>Rotura y reposición pavimento asfáltico</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-08-03T15:03:00</t>
+          <t>2026-08-03T15:04:02.44</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8323,12 +9778,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -8353,34 +9808,49 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2342-30-LP26</t>
+          <t>4487-29-LE26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO MULTICANCHAS CASAS DEL PARQUE III LA PORTADA Y CONSTRUCCIÓN SANTA BÁRBARA SAN BERNARDO</t>
+          <t>CONSERVACIÓN LICEO POLIVALENTE LA FRONTERA NEGRET</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -8388,7 +9858,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-03T15:01:00</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8404,12 +9874,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -8434,42 +9904,57 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3296-19-LE25</t>
+          <t>5194-3-LE26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Contratación AITO conservación camino no enrolados 8 sectores rurales Curaco de Vélez.</t>
+          <t>Adquisicion de Equipos Deportivos</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-01-08T19:55:00</t>
+          <t>2026-08-31T16:30:00</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8485,12 +9970,12 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -8515,34 +10000,49 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Certificación SEC (Chile)</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>4483-15-LR26</t>
+          <t>3296-19-LE25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>REPOSICION CUARTEL GENERAL 1° COMPAÑIA DE BOMBEROS TIERRA AMARILLA</t>
+          <t>Contratación AITO conservación camino no enrolados 8 sectores rurales Curaco de Vélez.</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -8550,7 +10050,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-06-30T15:30:00</t>
+          <t>2026-01-08T19:55:00</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -8596,42 +10096,57 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>4494-47-LE26</t>
+          <t>980313-25-LP26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN ESCUELA EDUARDO CAMPBELL PENCO</t>
+          <t>CONSTRUCCIÓN CANCHA PASTO SINTÉTICO VILLA PELUCA</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-08-18T15:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -8647,12 +10162,12 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -8677,42 +10192,57 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>584264-35-LR26</t>
+          <t>2760-100-LE26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SUM.SEÑALES DE TRANSITO DEMARCACIÓN INDEPENDENCIA</t>
+          <t>PRODUCCION Y DESARROLLO DE EVENTOS JORNADA FAMILIAR INTERACTIVA DE LOS DERECHOS DE LAS NIÑAS Y NIÑOS 2026</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-04T15:05:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -8728,12 +10258,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -8758,42 +10288,57 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Plataforma Interact</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>608897-45-LE26</t>
+          <t>2793-104-LE26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SISTEMATIZACIÓN DE INFORMACIÓN PARA LA IDENTIFICACIÓN DE PRIORIDADES DE CONSERVACIÓN MARINA PARA EL DISEÑO DE UNA RED DE ÁREAS MARINAS PROTEGIDAS EN LAS ECORREGIONES HUMBOLDTIANA CHILE CENTRAL ARAUCANA CHILOENSE Y CANALESFIORDOS DEL SUR DE CHILE</t>
+          <t>MANTENIMIENTO DE EQUIPOS Y SISTEMAS CLIMATIZACION</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-08-13T16:00:00</t>
+          <t>2026-08-03T15:01:00</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -8839,34 +10384,49 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>610-13-LP26</t>
+          <t>2981-204-LE26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Determinación del Estándar Metodológico para el Cálculo de Rotura y Reposición de Pavimentos en Redes de Distribución</t>
+          <t>SERVICIO DE MANTENIMIENTO DE CALDERAS</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -8874,7 +10434,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-08-21T15:00:00</t>
+          <t>2026-08-14T15:00:00</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -8920,34 +10480,49 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1481-5-L126</t>
+          <t>3084-15-R126</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>COMPRA DE ARTICULOS DE LIBRERIA, MATERIAL PEDAGOGICO, DEPORTIVO, ALIMENTACION Y ASEO SAAT - INSTITUTO DE EDUCACION PARA EL ADULTO RBD 40008-4</t>
+          <t>“ADQUISICIÓN DE LICENCIAS OFFICE LTSC PRO PLUS 2024 LICENCIAS MICROSOFT WINDOWS 11 PRO LICENCIAS WINDOWS EXCHANGE SERVER 2019 LICENCIAS WINDOWS SERVER 2025 STANDARD 16 CORES ESP Y LICENCIAS EXCHANGE SERVER STANDARD 2019 CAL SU EQUIVALENTE TÉCNICO O SU</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -8955,7 +10530,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-07-22T15:00:00</t>
+          <t>2026-06-03T15:00:00</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9001,34 +10576,49 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2467-79-LE26</t>
+          <t>3621-39-LE26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE CAMARAS DE SEGURIDAD PARA RECAMBIO</t>
+          <t>INSTALACION DE ALUMBRADO PUBLICO ORNAMENTAL PASEO</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -9036,7 +10626,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-08-03T15:20:00</t>
+          <t>2026-08-03T16:20:00</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9052,12 +10642,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Vial</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -9082,34 +10672,49 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>Cumple con Observación Comercial</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>Se sugiere incorporar opcionalmente telegestión Interact City para valor agregado en eficiencia energética.</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>RoadFlair / Xceed Pro: IP66, IK08, Zócalo Zhaga/NEMA, Interact City, CCT 3000K (DS1).</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2760-100-LE26</t>
+          <t>3693-141-CO26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PRODUCCION Y DESARROLLO DE EVENTOS JORNADA FAMILIAR INTERACTIVA DE LOS DERECHOS DE LAS NIÑAS Y NIÑOS 2026</t>
+          <t>CONSERVACIÓN Y HABILITACIÓN SALAS DE BOMBAS COMPLEJO EDUCACIONAL CLARA SOLOVERA COLEGIO EL QUISCO Y ESCUELA POETA NERUDA</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -9163,42 +10768,57 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>Plataforma Interact</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2793-104-LE26</t>
+          <t>407-86-LE26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE EQUIPOS Y SISTEMAS CLIMATIZACION</t>
+          <t>SERVICIO DE MANTENIMIENTO PREVENTIVO Y REPARATIVO SIN REPUESTOS PARA AUTOCLAVE</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-08-03T15:01:00</t>
+          <t>2026-08-03T10:53:14.54</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9244,42 +10864,57 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2981-204-LE26</t>
+          <t>4483-15-LR26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO DE CALDERAS</t>
+          <t>REPOSICION CUARTEL GENERAL 1° COMPAÑIA DE BOMBEROS TIERRA AMARILLA</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-08-14T15:00:00</t>
+          <t>2026-06-30T15:30:00</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9325,42 +10960,57 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3084-15-R126</t>
+          <t>4494-47-LE26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE LICENCIAS OFFICE LTSC PRO PLUS 2024 LICENCIAS MICROSOFT WINDOWS 11 PRO LICENCIAS WINDOWS EXCHANGE SERVER 2019 LICENCIAS WINDOWS SERVER 2025 STANDARD 16 CORES ESP Y LICENCIAS EXCHANGE SERVER STANDARD 2019 CAL SU EQUIVALENTE TÉCNICO O SU</t>
+          <t>CONSERVACIÓN ESCUELA EDUARDO CAMPBELL PENCO</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-06-03T15:00:00</t>
+          <t>2026-08-18T15:00:00</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9376,12 +11026,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -9406,42 +11056,57 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3621-39-LE26</t>
+          <t>584264-35-LR26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>INSTALACION DE ALUMBRADO PUBLICO ORNAMENTAL PASEO</t>
+          <t>SUM.SEÑALES DE TRANSITO DEMARCACIÓN INDEPENDENCIA</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-08-03T16:20:00</t>
+          <t>2026-09-04T15:05:00</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9457,12 +11122,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial y General)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -9487,42 +11152,57 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>Proyecto deportivo: Se recomienda Arena X con integración Interact Sports para cumplimiento IND y DS1.</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Arena X: IP66, IK08/09, Telegestión Interact Sports DMX/RDM, Ópticas Anti-glare DS1.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3693-141-CO26</t>
+          <t>608897-45-LE26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN Y HABILITACIÓN SALAS DE BOMBAS COMPLEJO EDUCACIONAL CLARA SOLOVERA COLEGIO EL QUISCO Y ESCUELA POETA NERUDA</t>
+          <t>SISTEMATIZACIÓN DE INFORMACIÓN PARA LA IDENTIFICACIÓN DE PRIORIDADES DE CONSERVACIÓN MARINA PARA EL DISEÑO DE UNA RED DE ÁREAS MARINAS PROTEGIDAS EN LAS ECORREGIONES HUMBOLDTIANA CHILE CENTRAL ARAUCANA CHILOENSE Y CANALESFIORDOS DEL SUR DE CHILE</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-13T16:00:00</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -9568,42 +11248,57 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>407-86-LE26</t>
+          <t>610-13-LP26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO PREVENTIVO Y REPARATIVO SIN REPUESTOS PARA AUTOCLAVE</t>
+          <t>Determinación del Estándar Metodológico para el Cálculo de Rotura y Reposición de Pavimentos en Redes de Distribución</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-08-03T10:53:14.54</t>
+          <t>2026-08-21T15:00:00</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -9649,22 +11344,37 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
@@ -9730,22 +11440,37 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>
@@ -9811,22 +11536,37 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>Sin requerimientos de control específicos</t>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>
       </c>
     </row>

--- a/agliluz/historial_licitaciones.xlsx
+++ b/agliluz/historial_licitaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD156"/>
+  <dimension ref="A1:AD158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,20 +583,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1658-85-LR26</t>
+          <t>3981-21-LE26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>P. 88-2026 “MEJORAMIENTO CANCHA DE FUTBOL MACROSECTOR BOTROLHUE TEMUCO”</t>
+          <t>INSTALACIÓN LUMINARIAS RUTA I-512 SECTOR LA CAPILLA COMUNA DE PAREDONES</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-20T15:30:00</t>
+          <t>2026-08-05T09:12:26.2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -618,12 +618,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / Canchas</t>
+          <t>Proyectores de Área / General</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>Proyectores de Área / CoreLine</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -703,13 +703,13 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -717,20 +717,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3729-53-LE26</t>
+          <t>771555-9-LP26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LUMINARIAS PUBLICAS</t>
+          <t>Mejoramiento Cancha de Futbol Fundina Norte RH</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-30T15:05:00</t>
+          <t>2026-08-05T10:00:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Proyectores de Área / General</t>
+          <t>Iluminación Deportiva / Canchas</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Proyectores de Área / CoreLine</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -837,13 +837,13 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -851,20 +851,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3938-24-LE26</t>
+          <t>1658-85-LR26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Luminarias Solares para la Seguridad Peatonal en Curarrehue</t>
+          <t>P. 88-2026 “MEJORAMIENTO CANCHA DE FUTBOL MACROSECTOR BOTROLHUE TEMUCO”</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-04T09:00:00</t>
+          <t>2026-05-20T15:30:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Luminarias Solares</t>
+          <t>Iluminación Deportiva / Canchas</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>GreenVision Solar (Autónoma)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -971,13 +971,13 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Sistema fotovoltaico autónomo: GreenVision Solar cumple con requerimientos fuera de red.</t>
+          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -985,12 +985,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5041-10-LP26</t>
+          <t>3729-53-LE26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Áridos con transporte mantención de Red Vial</t>
+          <t>LUMINARIAS PUBLICAS</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -998,7 +998,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-27T15:01:00</t>
+          <t>2026-06-30T15:05:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Iluminación Vial / Pública</t>
+          <t>Proyectores de Área / General</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
+          <t>Proyectores de Área / CoreLine</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1105,13 +1105,13 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1119,20 +1119,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1002-64-LE26</t>
+          <t>3938-24-LE26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CONVENIO SERVICIO DE ASEO DEPENDENCIAS DE VIALIDAD</t>
+          <t>Luminarias Solares para la Seguridad Peatonal en Curarrehue</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-13T16:00:00</t>
+          <t>2026-08-04T09:00:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Iluminación Vial / Pública</t>
+          <t>Luminarias Solares</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
+          <t>GreenVision Solar (Autónoma)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1239,13 +1239,13 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
+          <t>Sistema fotovoltaico autónomo: GreenVision Solar cumple con requerimientos fuera de red.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1253,20 +1253,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1200-18-LE26</t>
+          <t>5041-10-LP26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADQ. VESTUARIO DEPORTIVO JDE - IND ARAUCANÍA</t>
+          <t>Áridos con transporte mantención de Red Vial</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-14T15:40:00</t>
+          <t>2026-07-27T15:01:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / Canchas</t>
+          <t>Iluminación Vial / Pública</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1373,13 +1373,13 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -1387,20 +1387,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2409-47-LE26</t>
+          <t>1002-64-LE26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO DE PATIO Y MULTICANCHA ESCUELA ESPAÑA D-870 SEP</t>
+          <t>CONVENIO SERVICIO DE ASEO DEPENDENCIAS DE VIALIDAD</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-04T09:00:00</t>
+          <t>2026-07-13T16:00:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / Canchas</t>
+          <t>Iluminación Vial / Pública</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1507,13 +1507,13 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -1521,12 +1521,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3791-59-LE26</t>
+          <t>1200-18-LE26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO Y REPOSICION DE ALUMBRADO</t>
+          <t>ADQ. VESTUARIO DEPORTIVO JDE - IND ARAUCANÍA</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-14T12:14:00</t>
+          <t>2026-08-14T15:40:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Proyectores de Área / General</t>
+          <t>Iluminación Deportiva / Canchas</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Proyectores de Área / CoreLine</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1655,20 +1655,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2408-23-LE26</t>
+          <t>2409-47-LE26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Reparación y Mejoramiento de Espacios Deportivos</t>
+          <t>MEJORAMIENTO DE PATIO Y MULTICANCHA ESCUELA ESPAÑA D-870 SEP</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-04T08:57:21.043</t>
+          <t>2026-08-04T09:00:00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1789,12 +1789,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2483-214-LP26</t>
+          <t>3791-59-LE26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> “REPOSICIÓN MULTICANCHA VILLA SAN ENRIQUE COMUNA DE QUILICURA”</t>
+          <t>MEJORAMIENTO Y REPOSICION DE ALUMBRADO</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-24T15:00:00</t>
+          <t>2026-08-14T12:14:00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / Canchas</t>
+          <t>Proyectores de Área / General</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>Proyectores de Área / CoreLine</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1909,13 +1909,13 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -1923,20 +1923,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1658-162-LE26</t>
+          <t>2408-23-LE26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P.192-2026 ADQUISICIÓN DE PANTALLAS INTERACTIVAS PARA ESCUELA CAMPOS DEPORTIVOS</t>
+          <t>Reparación y Mejoramiento de Espacios Deportivos</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-04T12:00:00</t>
+          <t>2026-08-04T08:57:21.043</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Plataforma Interact</t>
+          <t>Control autónomo o estándar</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -2057,12 +2057,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1591-17-LE26</t>
+          <t>2483-214-LP26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ACTUALIZACIÓN DE RUTAS Y CIRCUITOS TURÍSTICOS VIALES EN LAS 5 MACROZONAS</t>
+          <t xml:space="preserve"> “REPOSICIÓN MULTICANCHA VILLA SAN ENRIQUE COMUNA DE QUILICURA”</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-17T15:00:00</t>
+          <t>2026-08-24T15:00:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2092,12 +2092,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Iluminación Vial / Pública</t>
+          <t>Iluminación Deportiva / Canchas</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2177,13 +2177,13 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
+          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -2191,20 +2191,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1658-146-LE26</t>
+          <t>1658-162-LE26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>P.160-2026 ADQUISICIÓN DE RING DE BOXEO PARA CENTRO DEPORTIVO DE CONTACTO”</t>
+          <t>P.192-2026 ADQUISICIÓN DE PANTALLAS INTERACTIVAS PARA ESCUELA CAMPOS DEPORTIVOS</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-01T16:00:00</t>
+          <t>2026-08-04T12:00:00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Control autónomo o estándar</t>
+          <t>Plataforma Interact</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -2317,7 +2317,7 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -2325,20 +2325,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2928-16-LE26</t>
+          <t>1591-17-LE26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO ALBERGUE ESTADIO MUNICIPAL DE QUELLÓN</t>
+          <t>ACTUALIZACIÓN DE RUTAS Y CIRCUITOS TURÍSTICOS VIALES EN LAS 5 MACROZONAS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-04T10:00:00</t>
+          <t>2026-08-17T15:00:00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / Canchas</t>
+          <t>Iluminación Vial / Pública</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2445,13 +2445,13 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -2459,20 +2459,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2424-139-LP25</t>
+          <t>1658-146-LE26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO NORMALIZACION SUMINISTRO E INSTALACION ELECTRICA EN CENTRO DEPORTIVO EL BOSQUE - 175 - 4777 </t>
+          <t>P.160-2026 ADQUISICIÓN DE RING DE BOXEO PARA CENTRO DEPORTIVO DE CONTACTO”</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-04T09:27:46.873</t>
+          <t>2026-07-01T16:00:00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2585,7 +2585,7 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -2593,20 +2593,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2455-32-LP26</t>
+          <t>2928-16-LE26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PLAN DE CONSERVACIÓN DE INFRAESTRUCTURA VIAL</t>
+          <t>MEJORAMIENTO ALBERGUE ESTADIO MUNICIPAL DE QUELLÓN</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-05T15:30:00</t>
+          <t>2026-08-04T10:00:00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Iluminación Vial / Pública</t>
+          <t>Iluminación Deportiva / Canchas</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2713,13 +2713,13 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
+          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -2727,20 +2727,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2490-53-LR26</t>
+          <t>2424-139-LP25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN Y OPERACIÓN DE PILETAS Y FUENTES DE AGUAS ORNAMENTALES COMUNA DE PROVIDENCIA</t>
+          <t xml:space="preserve">SERVICIO NORMALIZACION SUMINISTRO E INSTALACION ELECTRICA EN CENTRO DEPORTIVO EL BOSQUE - 175 - 4777 </t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-07T13:30:00</t>
+          <t>2026-08-04T09:27:46.873</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Iluminación Ornamental / Arquitectónica</t>
+          <t>Iluminación Deportiva / Canchas</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Tango Pro / Color Kinetics + Dynalite</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2847,13 +2847,13 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Control de iluminación dinámico: Dynalite y Color Kinetics garantizan gestión RGBW y DS1.</t>
+          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -2861,12 +2861,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3416-53-L126</t>
+          <t>2455-32-LP26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANTENIMIENTO Y REPARACIÓN DE CANCHAS DE TENIS </t>
+          <t>PLAN DE CONSERVACIÓN DE INFRAESTRUCTURA VIAL</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-29T16:00:00</t>
+          <t>2026-06-05T15:30:00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / Canchas</t>
+          <t>Iluminación Vial / Pública</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2981,13 +2981,13 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -2995,20 +2995,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3621-52-L126</t>
+          <t>2490-53-LR26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SERVIVIO REPARACION CIRCUITO DE ALUMBRADO PUBLICO</t>
+          <t>SERVICIO DE MANTENCIÓN Y OPERACIÓN DE PILETAS Y FUENTES DE AGUAS ORNAMENTALES COMUNA DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-10T15:30:00</t>
+          <t>2026-07-07T13:30:00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Iluminación Vial / Pública</t>
+          <t>Iluminación Ornamental / Arquitectónica</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
+          <t>Tango Pro / Color Kinetics + Dynalite</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -3115,13 +3115,13 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
+          <t>Control de iluminación dinámico: Dynalite y Color Kinetics garantizan gestión RGBW y DS1.</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr"/>
@@ -3129,20 +3129,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1133353-34-LE26</t>
+          <t>3416-53-L126</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MECANICA DE SUELOS PROYECTO CONSTRUCCION POLIDEPORTIVO RAUCO</t>
+          <t xml:space="preserve">MANTENIMIENTO Y REPARACIÓN DE CANCHAS DE TENIS </t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-07-29T16:00:00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3255,7 +3255,7 @@
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr"/>
@@ -3263,12 +3263,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1232565-25-L126</t>
+          <t>3621-52-L126</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Adquisición de Equipamiento Deportivos Proyecto ULS 2595</t>
+          <t>SERVIVIO REPARACION CIRCUITO DE ALUMBRADO PUBLICO</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-10T17:00:00</t>
+          <t>2026-08-10T15:30:00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / Canchas</t>
+          <t>Iluminación Vial / Pública</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr"/>
@@ -3397,12 +3397,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1288505-6-LE26</t>
+          <t>1133353-34-LE26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Adquisición de Equipos de Fotografía e iluminación</t>
+          <t>MECANICA DE SUELOS PROYECTO CONSTRUCCION POLIDEPORTIVO RAUCO</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-03T19:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Proyectores de Área / General</t>
+          <t>Iluminación Deportiva / Canchas</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Proyectores de Área / CoreLine</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -3531,20 +3531,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1506668-9-LE26</t>
+          <t>1232565-25-L126</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MATERIAL DEPORTIVO Y MATERIAL MUSICAL</t>
+          <t>Adquisición de Equipamiento Deportivos Proyecto ULS 2595</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-03T17:30:00</t>
+          <t>2026-08-10T17:00:00</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3657,7 +3657,7 @@
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr"/>
@@ -3665,20 +3665,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2007-2-LE26</t>
+          <t>1288505-6-LE26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Servicio de Vigilancia Vialidad San Felipe</t>
+          <t>Adquisición de Equipos de Fotografía e iluminación</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-10T15:00:00</t>
+          <t>2026-08-03T19:00:00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Iluminación Vial / Pública</t>
+          <t>Proyectores de Área / General</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
+          <t>Proyectores de Área / CoreLine</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3785,13 +3785,13 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr"/>
@@ -3799,12 +3799,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1211839-53-LE26</t>
+          <t>1506668-9-LE26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE MATERIALES E IMPLEMENTOS DEPORTIVOS</t>
+          <t>MATERIAL DEPORTIVO Y MATERIAL MUSICAL</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-03T17:30:00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3933,20 +3933,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1048-55-LE26</t>
+          <t>2007-2-LE26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ADQ. VESTUARIO Y EPP PERSONAL LUMINARIA 2do LLAMAD</t>
+          <t>Servicio de Vigilancia Vialidad San Felipe</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-10T15:00:00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Proyectores de Área / General</t>
+          <t>Iluminación Vial / Pública</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Proyectores de Área / CoreLine</t>
+          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -4053,13 +4053,13 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr"/>
@@ -4067,20 +4067,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2428-57-LE26</t>
+          <t>1211839-53-LE26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EQUIPAMIENTO DE AUDIO SONIDO E ILUMINACIÓN</t>
+          <t>ADQUISICIÓN DE MATERIALES E IMPLEMENTOS DEPORTIVOS</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-10T15:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Proyectores de Área / General</t>
+          <t>Iluminación Deportiva / Canchas</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Proyectores de Área / CoreLine</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -4187,13 +4187,13 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr"/>
@@ -4201,20 +4201,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2430-61-LR26</t>
+          <t>1048-55-LE26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>“REPOSICIÓN Y MANTENCIÓN SISTEMA DE AUDIO DEL ESTADIO REGIONAL CALVO Y BASCUÑAN ANTOFAGASTA”</t>
+          <t>ADQ. VESTUARIO Y EPP PERSONAL LUMINARIA 2do LLAMAD</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-17T11:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / Canchas</t>
+          <t>Proyectores de Área / General</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>Proyectores de Área / CoreLine</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -4321,13 +4321,13 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr"/>
@@ -4335,20 +4335,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3693-145-LE26</t>
+          <t>2428-57-LE26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE VESTUARIO DEPORTIVO PARA ESTUDIANTE</t>
+          <t>EQUIPAMIENTO DE AUDIO SONIDO E ILUMINACIÓN</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-08-10T15:00:00</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4370,12 +4370,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / Canchas</t>
+          <t>Proyectores de Área / General</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>Proyectores de Área / CoreLine</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -4455,13 +4455,13 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr"/>
@@ -4469,12 +4469,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1198-24-LE26</t>
+          <t>2430-61-LR26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mantención y Obras Menores Estadio San Felipe</t>
+          <t>“REPOSICIÓN Y MANTENCIÓN SISTEMA DE AUDIO DEL ESTADIO REGIONAL CALVO Y BASCUÑAN ANTOFAGASTA”</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-08-13T15:00:00</t>
+          <t>2026-09-17T11:00:00</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4595,7 +4595,7 @@
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr"/>
@@ -4603,12 +4603,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3920-23-LE26</t>
+          <t>3693-145-LE26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hacia una Villarrica Carbono Neutral: Árbol Solar</t>
+          <t>ADQUISICIÓN DE VESTUARIO DEPORTIVO PARA ESTUDIANTE</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Luminarias Solares</t>
+          <t>Iluminación Deportiva / Canchas</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>GreenVision Solar (Autónoma)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Sistema fotovoltaico autónomo: GreenVision Solar cumple con requerimientos fuera de red.</t>
+          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -4737,12 +4737,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5194-3-LE26</t>
+          <t>1198-24-LE26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Adquisicion de Equipos Deportivos</t>
+          <t>Mantención y Obras Menores Estadio San Felipe</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-08-31T16:30:00</t>
+          <t>2026-08-13T15:00:00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4863,7 +4863,7 @@
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr"/>
@@ -4871,12 +4871,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2735-110-LE26</t>
+          <t>3920-23-LE26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ELABORACIÓN DE MAPA SOLAR DEL ÁREA URBANA</t>
+          <t>Hacia una Villarrica Carbono Neutral: Árbol Solar</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -5005,20 +5005,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1481-5-L126</t>
+          <t>5194-3-LE26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>COMPRA DE ARTICULOS DE LIBRERIA, MATERIAL PEDAGOGICO, DEPORTIVO, ALIMENTACION Y ASEO SAAT - INSTITUTO DE EDUCACION PARA EL ADULTO RBD 40008-4</t>
+          <t>Adquisicion de Equipos Deportivos</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-22T15:00:00</t>
+          <t>2026-08-31T16:30:00</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -5131,7 +5131,7 @@
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr"/>
@@ -5139,20 +5139,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1225288-2-LE26</t>
+          <t>2735-110-LE26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IMPLEMENTACIÓN TALLERES DEPORTIVOS RECREATIVOS</t>
+          <t>ELABORACIÓN DE MAPA SOLAR DEL ÁREA URBANA</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-26T16:30:00</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -5174,12 +5174,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / Canchas</t>
+          <t>Luminarias Solares</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>GreenVision Solar (Autónoma)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -5259,13 +5259,13 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Sistema fotovoltaico autónomo: GreenVision Solar cumple con requerimientos fuera de red.</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr"/>
@@ -5273,12 +5273,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1225288-5-LE26</t>
+          <t>1481-5-L126</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IMPLEMENTACIÓN PARA APOYO CLUBES DEPORTIVOS</t>
+          <t>COMPRA DE ARTICULOS DE LIBRERIA, MATERIAL PEDAGOGICO, DEPORTIVO, ALIMENTACION Y ASEO SAAT - INSTITUTO DE EDUCACION PARA EL ADULTO RBD 40008-4</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-26T16:30:00</t>
+          <t>2026-07-22T15:00:00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5399,7 +5399,7 @@
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr"/>
@@ -5407,20 +5407,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3453-62-LE26</t>
+          <t>1225288-2-LE26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SERVICIO MANT YO REP DE PISO ILUMINACION Y BODEGA</t>
+          <t>IMPLEMENTACIÓN TALLERES DEPORTIVOS RECREATIVOS</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-06-26T16:30:00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Proyectores de Área / General</t>
+          <t>Iluminación Deportiva / Canchas</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Proyectores de Área / CoreLine</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Hitos críticos en bases técnicas</t>
+          <t>Conforme a cronograma oficial</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -5527,13 +5527,13 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr"/>
@@ -5541,20 +5541,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3562-31-LR26</t>
+          <t>1225288-5-LE26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN ESTADIO DE PUEBLO NUEVO LA CALERA</t>
+          <t>IMPLEMENTACIÓN PARA APOYO CLUBES DEPORTIVOS</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-03T16:00:00</t>
+          <t>2026-06-26T16:30:00</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5667,7 +5667,7 @@
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr"/>
@@ -5675,20 +5675,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3938-25-LE26</t>
+          <t>3453-62-LE26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mejoramiento Cierre Perimetral Recinto Deportivo Catripulli</t>
+          <t>SERVICIO MANT YO REP DE PISO ILUMINACION Y BODEGA</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-21T16:20:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / Canchas</t>
+          <t>Proyectores de Área / General</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>Proyectores de Área / CoreLine</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Conforme a cronograma oficial</t>
+          <t>Hitos críticos en bases técnicas</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -5795,13 +5795,13 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr"/>
@@ -5809,20 +5809,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3968-35-LE26</t>
+          <t>3562-31-LR26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>UNIFORMES DEPORTIVOS ESC. MONSEÑOR MANUEL LARRAIN</t>
+          <t>CONSERVACIÓN ESTADIO DE PUEBLO NUEVO LA CALERA</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-09-03T16:00:00</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5935,7 +5935,7 @@
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr"/>
@@ -5943,12 +5943,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4118-5-LP26</t>
+          <t>3938-25-LE26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ALUMBRADO PÚBLICO SECTOR COMUNA SANTA INÉS</t>
+          <t>Mejoramiento Cierre Perimetral Recinto Deportivo Catripulli</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-08-25T12:00:00</t>
+          <t>2026-08-21T16:20:00</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Iluminación Vial / Pública</t>
+          <t>Iluminación Deportiva / Canchas</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -6063,13 +6063,13 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
+          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr"/>
@@ -6077,12 +6077,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>979-35-LE26</t>
+          <t>3968-35-LE26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Adquisición de un 1 servidor de aplicaciones de alto rendimiento para la Dirección de Vialidad.</t>
+          <t>UNIFORMES DEPORTIVOS ESC. MONSEÑOR MANUEL LARRAIN</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-03T15:01:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Iluminación Vial / Pública</t>
+          <t>Iluminación Deportiva / Canchas</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
+          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr"/>
@@ -6211,20 +6211,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>980313-25-LP26</t>
+          <t>4118-5-LP26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN CANCHA PASTO SINTÉTICO VILLA PELUCA</t>
+          <t>ALUMBRADO PÚBLICO SECTOR COMUNA SANTA INÉS</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-25T12:00:00</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / Canchas</t>
+          <t>Iluminación Vial / Pública</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -6331,13 +6331,13 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr"/>
@@ -6345,12 +6345,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2760-100-LE26</t>
+          <t>979-35-LE26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PRODUCCION Y DESARROLLO DE EVENTOS JORNADA FAMILIAR INTERACTIVA DE LOS DERECHOS DE LAS NIÑAS Y NIÑOS 2026</t>
+          <t>Adquisición de un 1 servidor de aplicaciones de alto rendimiento para la Dirección de Vialidad.</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-03T15:01:00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Proyectores de Área / General</t>
+          <t>Iluminación Vial / Pública</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Proyectores de Área / CoreLine</t>
+          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Plataforma Interact</t>
+          <t>Control autónomo o estándar</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr"/>
@@ -6479,12 +6479,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3621-39-LE26</t>
+          <t>980313-25-LP26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>INSTALACION DE ALUMBRADO PUBLICO ORNAMENTAL PASEO</t>
+          <t>CONSTRUCCIÓN CANCHA PASTO SINTÉTICO VILLA PELUCA</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-03T16:20:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Iluminación Vial / Pública</t>
+          <t>Iluminación Deportiva / Canchas</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
+          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr"/>
@@ -6613,12 +6613,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2274-30-LE26</t>
+          <t>2760-100-LE26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PROPUESTA PUBLICA ADQUISICION MATERIAL DE ENSEÑANZA E INSUMOS DEPORTIVOS CONVENIO LA PINTANA 2026 EXP. 11856</t>
+          <t>PRODUCCION Y DESARROLLO DE EVENTOS JORNADA FAMILIAR INTERACTIVA DE LOS DERECHOS DE LAS NIÑAS Y NIÑOS 2026</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-08-03T18:40:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -6648,12 +6648,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / Canchas</t>
+          <t>Proyectores de Área / General</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>Proyectores de Área / CoreLine</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Normativa DS1 / Estándar</t>
+          <t>Certificación SEC</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Control autónomo o estándar</t>
+          <t>Plataforma Interact</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr"/>
@@ -6747,12 +6747,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2328-46-LE26</t>
+          <t>3621-39-LE26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA E-55 ADQUISICION DE CALZADO DEPORTIVO JARDINES INFANTILES DEPENDIENTES DEL DAEM DE PUERTO MONTT</t>
+          <t>INSTALACION DE ALUMBRADO PUBLICO ORNAMENTAL PASEO</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-03T16:20:00</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / Canchas</t>
+          <t>Iluminación Vial / Pública</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Normativa DS1 / Estándar</t>
+          <t>Certificación SEC</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr"/>
@@ -6881,12 +6881,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>750998-47-LP26</t>
+          <t>2274-30-LE26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>REPOSICIÓN CANCHA DE BABY FUTBOL CD LOS 56 UNIDOS</t>
+          <t>PROPUESTA PUBLICA ADQUISICION MATERIAL DE ENSEÑANZA E INSUMOS DEPORTIVOS CONVENIO LA PINTANA 2026 EXP. 11856</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-03T15:15:00</t>
+          <t>2026-08-03T18:40:00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -7015,20 +7015,20 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>967490-14-LE26</t>
+          <t>2328-46-LE26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MANT. Y REP. CANCHA DE ALTO RENDIMIENTO CABALLERÍA</t>
+          <t>LICITACIÓN PÚBLICA E-55 ADQUISICION DE CALZADO DEPORTIVO JARDINES INFANTILES DEPENDIENTES DEL DAEM DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-21T15:30:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -7141,7 +7141,7 @@
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr"/>
@@ -7149,12 +7149,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3508-27-LE26</t>
+          <t>750998-47-LP26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE TRABAJOS VIALES</t>
+          <t>REPOSICIÓN CANCHA DE BABY FUTBOL CD LOS 56 UNIDOS</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-03T15:01:00</t>
+          <t>2026-08-03T15:15:00</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -7184,12 +7184,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Iluminación Vial / Pública</t>
+          <t>Iluminación Deportiva / Canchas</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
+          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr"/>
@@ -7283,20 +7283,20 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4301-33-LR26</t>
+          <t>967490-14-LE26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>provisión y mantención de macetas ornamentales</t>
+          <t>MANT. Y REP. CANCHA DE ALTO RENDIMIENTO CABALLERÍA</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-05-26T09:00:00</t>
+          <t>2026-08-21T15:30:00</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -7318,12 +7318,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Iluminación Ornamental / Arquitectónica</t>
+          <t>Iluminación Deportiva / Canchas</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Tango Pro / Color Kinetics + Dynalite</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -7403,13 +7403,13 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>Control de iluminación dinámico: Dynalite y Color Kinetics garantizan gestión RGBW y DS1.</t>
+          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr"/>
@@ -7417,12 +7417,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2322-53-LR26</t>
+          <t>3508-27-LE26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construcción Cancha de Pasto Sintetico Meseta Azul  Vallenar </t>
+          <t>CONVENIO DE SUMINISTRO DE TRABAJOS VIALES</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-08-03T15:01:00</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -7452,12 +7452,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / Canchas</t>
+          <t>Iluminación Vial / Pública</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr"/>
@@ -7551,20 +7551,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2342-30-LP26</t>
+          <t>4301-33-LR26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO MULTICANCHAS CASAS DEL PARQUE III LA PORTADA Y CONSTRUCCIÓN SANTA BÁRBARA SAN BERNARDO</t>
+          <t>provisión y mantención de macetas ornamentales</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-05-26T09:00:00</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -7586,12 +7586,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / Canchas</t>
+          <t>Iluminación Ornamental / Arquitectónica</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>Tango Pro / Color Kinetics + Dynalite</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -7671,13 +7671,13 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Control de iluminación dinámico: Dynalite y Color Kinetics garantizan gestión RGBW y DS1.</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr"/>
@@ -7685,20 +7685,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2345-127-LE26</t>
+          <t>2322-53-LR26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ARTÍCULOS DEPORTIVOS</t>
+          <t xml:space="preserve">Construcción Cancha de Pasto Sintetico Meseta Azul  Vallenar </t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-17T15:01:00</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -7811,7 +7811,7 @@
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr"/>
@@ -7819,20 +7819,20 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3562-28-LR26</t>
+          <t>2342-30-LP26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN COMPLEJO DEPORTIVO ESPERANZA CALERA</t>
+          <t>MEJORAMIENTO MULTICANCHAS CASAS DEL PARQUE III LA PORTADA Y CONSTRUCCIÓN SANTA BÁRBARA SAN BERNARDO</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-03T16:37:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -7945,7 +7945,7 @@
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr"/>
@@ -7953,12 +7953,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4412-20-LP26</t>
+          <t>2345-127-LE26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO MULTICANCHAS EL RETIRO Y TUCUQUERE</t>
+          <t>ADQUISICIÓN DE ARTÍCULOS DEPORTIVOS</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-02T15:30:00</t>
+          <t>2026-08-17T15:01:00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -8079,7 +8079,7 @@
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr"/>
@@ -8087,20 +8087,20 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>996-22-LE26</t>
+          <t>3562-28-LR26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SERVICIO DE ASEO DEPENDENCIAS VIALIDAD PROVINCIA DE CHOAPA</t>
+          <t>CONSERVACIÓN COMPLEJO DEPORTIVO ESPERANZA CALERA</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-03T16:00:00</t>
+          <t>2026-09-03T16:37:00</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -8122,12 +8122,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Iluminación Vial / Pública</t>
+          <t>Iluminación Deportiva / Canchas</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -8207,13 +8207,13 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
+          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr"/>
@@ -8221,12 +8221,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1191688-58-LP26</t>
+          <t>4412-20-LP26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mejoramiento vial de diversas calzadas etapa 3</t>
+          <t>MEJORAMIENTO MULTICANCHAS EL RETIRO Y TUCUQUERE</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-24T15:30:00</t>
+          <t>2026-09-02T15:30:00</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Iluminación Vial / Pública</t>
+          <t>Iluminación Deportiva / Canchas</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -8341,13 +8341,13 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
+          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr"/>
@@ -8355,20 +8355,20 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1202333-49-LP26</t>
+          <t>996-22-LE26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN DE REDES DE AGUA POTABLE Y ALCANTARILLADO CALLES AMALIA VIAL Y AGUSTÍN MORENO QUINTERO</t>
+          <t>SERVICIO DE ASEO DEPENDENCIAS VIALIDAD PROVINCIA DE CHOAPA</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-11T17:00:00</t>
+          <t>2026-08-03T16:00:00</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -8481,7 +8481,7 @@
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr"/>
@@ -8489,20 +8489,20 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1658-151-LP26</t>
+          <t>1191688-58-LP26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>P.168-2026 OBRAS DE IMPERMEABILIZACIÓN DE GRADERÍAS TRIBUNA PACÍFICO ESTADIO MUNICIPAL GERMÁN BECKER TEMUCO</t>
+          <t>Mejoramiento vial de diversas calzadas etapa 3</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-08-24T15:30:00</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -8524,12 +8524,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / Canchas</t>
+          <t>Iluminación Vial / Pública</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -8609,13 +8609,13 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr"/>
@@ -8623,20 +8623,20 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2788-33-LP26</t>
+          <t>1202333-49-LP26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>REPOSICIÓN MULTICANCHA VILLA LAS AMÉRICAS I PAINE</t>
+          <t>CONSTRUCCIÓN DE REDES DE AGUA POTABLE Y ALCANTARILLADO CALLES AMALIA VIAL Y AGUSTÍN MORENO QUINTERO</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-03T15:01:00</t>
+          <t>2026-06-11T17:00:00</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -8658,12 +8658,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / Canchas</t>
+          <t>Iluminación Vial / Pública</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -8743,13 +8743,13 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr"/>
@@ -8757,20 +8757,20 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>673663-15-LP26</t>
+          <t>1658-151-LP26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN RED ALUMBRADO PÚBLICO Y LUMINARIAS SO</t>
+          <t>P.168-2026 OBRAS DE IMPERMEABILIZACIÓN DE GRADERÍAS TRIBUNA PACÍFICO ESTADIO MUNICIPAL GERMÁN BECKER TEMUCO</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-03T13:18:45.21</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Iluminación Vial / Pública</t>
+          <t>Iluminación Deportiva / Canchas</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
+          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr"/>
@@ -8891,12 +8891,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1085111-21-LR26</t>
+          <t>2788-33-LP26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN MANT Y SEG PARQUE MONUM CHILLAN VIEJO</t>
+          <t>REPOSICIÓN MULTICANCHA VILLA LAS AMÉRICAS I PAINE</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -8904,30 +8904,34 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-03T16:00:00</t>
+          <t>2026-08-03T15:01:00</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>No especificado / En proceso</t>
+          <t>En curso (&lt; 10 días / Vigente)</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>0</v>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>50000000</v>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / Canchas</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -8942,27 +8946,27 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>No especificado en bases</t>
+          <t>100W - 250W (Estimado Bases)</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>No especificado en bases</t>
+          <t>12,000 lm - 24,000 lm (Estimado Bases)</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>IP66 Requerido</t>
+          <t>IP66</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>IK08 Requerido</t>
+          <t>IK08</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Certificación SEC (Chile)</t>
+          <t>Normativa DS1 / Estándar</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -8982,12 +8986,12 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>Garantía de seriedad de oferta y fiel cumplimiento estándar</t>
+          <t>Garantía estándar según bases</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Conforme a cronograma oficial de bases</t>
+          <t>Conforme a cronograma oficial</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
@@ -8997,7 +9001,7 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>Aplicación de multas por atraso estándar MOP/Mercado Público</t>
+          <t>Multas estándar por atraso MOP/Mercado Público</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
@@ -9007,7 +9011,7 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr"/>
@@ -9021,43 +9025,47 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1263503-4-O126</t>
+          <t>673663-15-LP26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA IV</t>
+          <t>CONSTRUCCIÓN RED ALUMBRADO PÚBLICO Y LUMINARIAS SO</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-03T11:07:24.06</t>
+          <t>2026-08-03T13:18:45.21</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>No especificado / En proceso</t>
+          <t>En curso (&lt; 10 días / Vigente)</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>0</v>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>50000000</v>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Vial / Pública</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial)</t>
+          <t>RoadFlair / Xceed Pro + Interact City (Telegestión Vial)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -9072,27 +9080,27 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>No especificado en bases</t>
+          <t>100W - 250W (Estimado Bases)</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>No especificado en bases</t>
+          <t>12,000 lm - 24,000 lm (Estimado Bases)</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>IP66 Requerido</t>
+          <t>IP66</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>IK08 Requerido</t>
+          <t>IK08</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Certificación SEC (Chile)</t>
+          <t>Normativa DS1 / Estándar</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -9112,12 +9120,12 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>Garantía de seriedad de oferta y fiel cumplimiento estándar</t>
+          <t>Garantía estándar según bases</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Conforme a cronograma oficial de bases</t>
+          <t>Conforme a cronograma oficial</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
@@ -9127,7 +9135,7 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>Aplicación de multas por atraso estándar MOP/Mercado Público</t>
+          <t>Multas estándar por atraso MOP/Mercado Público</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
@@ -9137,7 +9145,7 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Licitación vial: Se recomienda RoadFlair con opción de telegestión Interact City.</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr"/>
@@ -9151,20 +9159,20 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1186-2-LE26</t>
+          <t>1085111-21-LR26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO DE ASCENSORES</t>
+          <t>CONSERVACIÓN MANT Y SEG PARQUE MONUM CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-13T15:00:00</t>
+          <t>2026-08-03T16:00:00</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -9273,7 +9281,7 @@
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr"/>
@@ -9281,12 +9289,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1263503-1-O126</t>
+          <t>1263503-4-O126</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA I</t>
+          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA IV</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -9294,7 +9302,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-08-03T10:51:48.64</t>
+          <t>2026-08-03T11:07:24.06</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -9411,12 +9419,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1306643-23-LE26</t>
+          <t>1186-2-LE26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SERVICIO DE REPOSICIÓN MAMPARAS CESFAM</t>
+          <t>SERVICIO DE MANTENIMIENTO DE ASCENSORES</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -9424,7 +9432,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-18T15:00:00</t>
+          <t>2026-08-13T15:00:00</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -9533,7 +9541,7 @@
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr"/>
@@ -9541,20 +9549,20 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1434-21-LE26</t>
+          <t>1263503-1-O126</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE EQUIPOS DENTALES</t>
+          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA I</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-08-17T15:01:00</t>
+          <t>2026-08-03T10:51:48.64</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -9663,7 +9671,7 @@
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr"/>
@@ -9671,20 +9679,20 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2157-78-LP26</t>
+          <t>1306643-23-LE26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CONVENIO DE MANTENIMIENTO PREVENTIVO Y CORRECTIVO PARA GRUPOS ELECTRÓGENOS FG WILSON 900KVA PERTENECIENTES AL HTC</t>
+          <t>SERVICIO DE REPOSICIÓN MAMPARAS CESFAM</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-08-03T17:19:08.62</t>
+          <t>2026-08-18T15:00:00</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -9793,7 +9801,7 @@
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr"/>
@@ -9801,20 +9809,20 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2183-9-LP26</t>
+          <t>1434-21-LE26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO SEMESTRAL EQUIPOS DE CLIMATIZACIÓN</t>
+          <t>MANTENIMIENTO DE EQUIPOS DENTALES</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-03T15:47:10.15</t>
+          <t>2026-08-17T15:01:00</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -9923,7 +9931,7 @@
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr"/>
@@ -9931,20 +9939,20 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2261-21-O126</t>
+          <t>2157-78-LP26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Conservación camino Antiguo Angol Los Sauces, Región de La Araucanía</t>
+          <t>CONVENIO DE MANTENIMIENTO PREVENTIVO Y CORRECTIVO PARA GRUPOS ELECTRÓGENOS FG WILSON 900KVA PERTENECIENTES AL HTC</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-03T09:00:00</t>
+          <t>2026-08-03T17:19:08.62</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -10053,7 +10061,7 @@
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr"/>
@@ -10061,20 +10069,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1057472-84-LP26</t>
+          <t>2183-9-LP26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CONVENIO DE MANTENIMIENTO PARA AUTOCLAVE STERRAD</t>
+          <t>MANTENIMIENTO SEMESTRAL EQUIPOS DE CLIMATIZACIÓN</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-07T16:00:00</t>
+          <t>2026-08-03T15:47:10.15</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -10183,7 +10191,7 @@
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr"/>
@@ -10191,20 +10199,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1057489-205-LP26</t>
+          <t>2261-21-O126</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convenio de Suministro de Insumos para detección de Autoanticuerpos mediante Inmunofluorescencia Indirecta con incorporación de equipamiento por 48 meses en el Hospital del Salvador </t>
+          <t>Conservación camino Antiguo Angol Los Sauces, Región de La Araucanía</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-03T17:00:00</t>
+          <t>2026-09-03T09:00:00</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -10222,12 +10230,12 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -10307,13 +10315,13 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr"/>
@@ -10321,20 +10329,20 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1057545-92-LE26</t>
+          <t>1057472-84-LP26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Convenio de suministro para mantenimiento de bombas hidráulicas y accesorios para establecimientos dependientes del Servicio de Salud Los Ríos</t>
+          <t>CONVENIO DE MANTENIMIENTO PARA AUTOCLAVE STERRAD</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-19T09:00:00</t>
+          <t>2026-07-07T16:00:00</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -10443,7 +10451,7 @@
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr"/>
@@ -10451,12 +10459,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1150-14-O126</t>
+          <t>1057489-205-LP26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Conservación Cauces Naturales Rio Clarillo 2026</t>
+          <t xml:space="preserve">Convenio de Suministro de Insumos para detección de Autoanticuerpos mediante Inmunofluorescencia Indirecta con incorporación de equipamiento por 48 meses en el Hospital del Salvador </t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -10464,7 +10472,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-03T17:00:00</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -10482,12 +10490,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -10567,7 +10575,7 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr"/>
@@ -10581,20 +10589,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1180703-19-LP26</t>
+          <t>1057545-92-LE26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>REPOSICIÓN DE EQUIPOS MÉDICO PARA SCR NEONATOLOGÍA PARA HOSPITAL DR. JUAN NOÉ CREVANI CÓDIGO BIP 40070708-0</t>
+          <t>Convenio de suministro para mantenimiento de bombas hidráulicas y accesorios para establecimientos dependientes del Servicio de Salud Los Ríos</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-08-19T09:00:00</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -10703,7 +10711,7 @@
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr"/>
@@ -10711,20 +10719,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1180919-7-LR26</t>
+          <t>1150-14-O126</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Reposición Posta de Salud Peñasmo Calbuco</t>
+          <t>Conservación Cauces Naturales Rio Clarillo 2026</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-06-24T16:30:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -10833,7 +10841,7 @@
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr"/>
@@ -10841,20 +10849,20 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1057472-9-LP26</t>
+          <t>1180703-19-LP26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CONVENIO DE MANTENIMIENTO TOMÓGRAFO COMPUTARIZADO</t>
+          <t>REPOSICIÓN DE EQUIPOS MÉDICO PARA SCR NEONATOLOGÍA PARA HOSPITAL DR. JUAN NOÉ CREVANI CÓDIGO BIP 40070708-0</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-18T16:00:00</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -10963,7 +10971,7 @@
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr"/>
@@ -10971,20 +10979,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1263503-3-O126</t>
+          <t>1180919-7-LR26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA III</t>
+          <t>Reposición Posta de Salud Peñasmo Calbuco</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-08-03T11:05:52.27</t>
+          <t>2026-06-24T16:30:00</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -11093,7 +11101,7 @@
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr"/>
@@ -11101,20 +11109,20 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1216085-36-LE26</t>
+          <t>1057472-9-LP26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO ASCENSORES</t>
+          <t>CONVENIO DE MANTENIMIENTO TOMÓGRAFO COMPUTARIZADO</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-06-26T15:30:00</t>
+          <t>2026-08-18T16:00:00</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -11223,7 +11231,7 @@
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr"/>
@@ -11231,20 +11239,20 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1537592-4-LE26</t>
+          <t>1263503-3-O126</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Adquisición de Herramientas Instrumentos y Equipos Especializados para Mantenimiento Industrial</t>
+          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA III</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-08-13T16:17:00</t>
+          <t>2026-08-03T11:05:52.27</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -11262,12 +11270,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -11347,13 +11355,13 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD82" t="inlineStr"/>
@@ -11361,20 +11369,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1537592-5-LE26</t>
+          <t>1216085-36-LE26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Adquisición de insumos de ferretería pintura limpieza y mantenimiento - LBV</t>
+          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO ASCENSORES</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-08-13T18:48:00</t>
+          <t>2026-06-26T15:30:00</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -11483,7 +11491,7 @@
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr"/>
@@ -11491,12 +11499,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2704-57-LP26</t>
+          <t>1537592-4-LE26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SC 3935 Servicio Mantenimiento prev y Correctivo de Calderas estufas de Tiro Balanceado termos</t>
+          <t>Adquisición de Herramientas Instrumentos y Equipos Especializados para Mantenimiento Industrial</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -11504,7 +11512,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-08-13T20:00:00</t>
+          <t>2026-08-13T16:17:00</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -11522,12 +11530,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -11607,7 +11615,7 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr"/>
@@ -11621,12 +11629,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2792-9-L126</t>
+          <t>1537592-5-LE26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>REPOSICIÓN DE SILLÓN DENTAL PARA CESFAM LA PINCOYA</t>
+          <t>Adquisición de insumos de ferretería pintura limpieza y mantenimiento - LBV</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -11634,7 +11642,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-08-13T09:00:00</t>
+          <t>2026-08-13T18:48:00</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -11751,12 +11759,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3416-45-L126</t>
+          <t>2704-57-LP26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERV. DE MANTENIMIENTO Y REPARACIÓN DE EQUIPOS </t>
+          <t>SC 3935 Servicio Mantenimiento prev y Correctivo de Calderas estufas de Tiro Balanceado termos</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -11764,7 +11772,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-08-10T15:30:00</t>
+          <t>2026-08-13T20:00:00</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -11822,7 +11830,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -11873,7 +11881,7 @@
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD86" t="inlineStr"/>
@@ -11881,20 +11889,20 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3296-1-LE26</t>
+          <t>2792-9-L126</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Contratación AITO conservación camino no enrolados 4 sectores rurales Curaco de Vélez.</t>
+          <t>REPOSICIÓN DE SILLÓN DENTAL PARA CESFAM LA PINCOYA</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-01-16T09:00:00</t>
+          <t>2026-08-13T09:00:00</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -12003,7 +12011,7 @@
       <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr"/>
@@ -12011,20 +12019,20 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1650-13-L126</t>
+          <t>3416-45-L126</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Servicio de Ejecución Intervenciones Psicosociales Grupales Comunitarias y Gestión Clínica para el Programa de Salud Mental - Hospital Clorinda Avello de Santa Juana</t>
+          <t xml:space="preserve">SERV. DE MANTENIMIENTO Y REPARACIÓN DE EQUIPOS </t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-03T15:48:00</t>
+          <t>2026-08-10T15:30:00</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -12042,12 +12050,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -12127,13 +12135,13 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr"/>
@@ -12141,20 +12149,20 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2186-21-LE26</t>
+          <t>3296-1-LE26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO PARA CALDERAS</t>
+          <t>Contratación AITO conservación camino no enrolados 4 sectores rurales Curaco de Vélez.</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-08-18T12:00:00</t>
+          <t>2026-01-16T09:00:00</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -12212,7 +12220,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -12263,7 +12271,7 @@
       <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AD89" t="inlineStr"/>
@@ -12271,20 +12279,20 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2292-35-LE26</t>
+          <t>1650-13-L126</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO DE EQUIPOS CRITICOS DE LOS ESTABLECIMIENTOS DE SALUD DE APS DE LA COMUNA DE TALCA</t>
+          <t>Servicio de Ejecución Intervenciones Psicosociales Grupales Comunitarias y Gestión Clínica para el Programa de Salud Mental - Hospital Clorinda Avello de Santa Juana</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-08-13T15:00:00</t>
+          <t>2026-08-03T15:48:00</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -12302,12 +12310,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -12387,13 +12395,13 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD90" t="inlineStr"/>
@@ -12401,20 +12409,20 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1057472-87-LP26</t>
+          <t>2186-21-LE26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CONVENIO DE MANTENIMIENTO PARA LAVACHATAS MEIKO</t>
+          <t>MANTENIMIENTO PREVENTIVO PARA CALDERAS</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-07-07T16:00:00</t>
+          <t>2026-08-18T12:00:00</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -12523,7 +12531,7 @@
       <c r="AB91" t="inlineStr"/>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AD91" t="inlineStr"/>
@@ -12531,12 +12539,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1133353-35-LP26</t>
+          <t>2292-35-LE26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE MATERIALES DE CONSTRUCCIÓN PARA MANTENIMIENTO DE EDIFICIOS MUNICIPALES EMERGENCIA Y APOYO SOCIAL DE LA MUNICIPALIDAD DE RAUCO</t>
+          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO DE EQUIPOS CRITICOS DE LOS ESTABLECIMIENTOS DE SALUD DE APS DE LA COMUNA DE TALCA</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -12544,7 +12552,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-08-13T17:30:00</t>
+          <t>2026-08-13T15:00:00</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -12661,20 +12669,20 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1199-11-LE26</t>
+          <t>1057472-87-LP26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Mantener y Reparar Aire acondicionado IND MAULE</t>
+          <t>CONVENIO DE MANTENIMIENTO PARA LAVACHATAS MEIKO</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-08-03T17:00:00</t>
+          <t>2026-07-07T16:00:00</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -12692,12 +12700,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -12777,13 +12785,13 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr"/>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AD93" t="inlineStr"/>
@@ -12791,12 +12799,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1369-14-O126</t>
+          <t>1133353-35-LP26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONSERVACIÓN CAMINOS BÁSICOS B-383, CRUCE 23 CH, LAGUNA MISCANTI, PROV. EL </t>
+          <t>CONVENIO DE SUMINISTRO DE MATERIALES DE CONSTRUCCIÓN PARA MANTENIMIENTO DE EDIFICIOS MUNICIPALES EMERGENCIA Y APOYO SOCIAL DE LA MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -12804,7 +12812,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-07T18:00:00</t>
+          <t>2026-08-13T17:30:00</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -12913,7 +12921,7 @@
       <c r="AB94" t="inlineStr"/>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD94" t="inlineStr"/>
@@ -12921,20 +12929,20 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1057472-85-LP26</t>
+          <t>1199-11-LE26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CONVENIO MANTENIMIENTO EQUIPOS Y TORRES ENDOSCOPIA</t>
+          <t>Mantener y Reparar Aire acondicionado IND MAULE</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-07-07T16:00:00</t>
+          <t>2026-08-03T17:00:00</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -12952,12 +12960,12 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -13037,13 +13045,13 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr"/>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD95" t="inlineStr"/>
@@ -13051,20 +13059,20 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1233616-49-LE26</t>
+          <t>1369-14-O126</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO IMPRESORAS Y MULTIFUNCIONALES EE.EE</t>
+          <t xml:space="preserve">CONSERVACIÓN CAMINOS BÁSICOS B-383, CRUCE 23 CH, LAGUNA MISCANTI, PROV. EL </t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-09-07T18:00:00</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -13173,7 +13181,7 @@
       <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AD96" t="inlineStr"/>
@@ -13181,20 +13189,20 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1233616-51-L126</t>
+          <t>1057472-85-LP26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO TORRES DE COMUNICACIÓN ARRIOSTRADA</t>
+          <t>CONVENIO MANTENIMIENTO EQUIPOS Y TORRES ENDOSCOPIA</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-08-03T15:04:02.473</t>
+          <t>2026-07-07T16:00:00</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -13303,7 +13311,7 @@
       <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr"/>
@@ -13311,20 +13319,20 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2744-26-L126</t>
+          <t>1233616-49-LE26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO INTEGRAL DE AUTOCLAVE</t>
+          <t>MANTENIMIENTO IMPRESORAS Y MULTIFUNCIONALES EE.EE</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-08-10T15:47:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -13433,7 +13441,7 @@
       <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr"/>
@@ -13441,12 +13449,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>3326-35-LE26</t>
+          <t>1233616-51-L126</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN E INSTALACIÓN DE ACCESORIO PARA EL VEHÍCULO FISCAL AC-2429 MARCA NISSAN MODELO PATHFINDER AÑO 2026 DE CARGO DE LA SUBDIRECCIÓN GENERAL SEGÚN BASES ADMINISTRATIVAS Y TÉCNICAS</t>
+          <t>MANTENIMIENTO TORRES DE COMUNICACIÓN ARRIOSTRADA</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -13454,7 +13462,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-03T18:03:05.86</t>
+          <t>2026-08-03T15:04:02.473</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -13472,12 +13480,12 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial)</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -13557,7 +13565,7 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr"/>
@@ -13571,12 +13579,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3882-71-LE26</t>
+          <t>2744-26-L126</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>REPOSICIÓN SISTEMA ELÉCTRICO CENTRAL DE CÁMARAS COMUNA DE LLAY LLAY</t>
+          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO INTEGRAL DE AUTOCLAVE</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -13584,7 +13592,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-08-17T15:00:00</t>
+          <t>2026-08-10T15:47:00</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -13693,7 +13701,7 @@
       <c r="AB100" t="inlineStr"/>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AD100" t="inlineStr"/>
@@ -13701,20 +13709,20 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>407-101-LP26</t>
+          <t>3326-35-LE26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO Y REPARATIVO SIN REPUESTOS PARA ECÓGRAFOS</t>
+          <t>ADQUISICIÓN E INSTALACIÓN DE ACCESORIO PARA EL VEHÍCULO FISCAL AC-2429 MARCA NISSAN MODELO PATHFINDER AÑO 2026 DE CARGO DE LA SUBDIRECCIÓN GENERAL SEGÚN BASES ADMINISTRATIVAS Y TÉCNICAS</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-08-03T18:03:05.86</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -13732,12 +13740,12 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -13817,7 +13825,7 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr"/>
@@ -13831,20 +13839,20 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>4366-22-LP26</t>
+          <t>3882-71-LE26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Rotura y reposición pavimento asfáltico</t>
+          <t>REPOSICIÓN SISTEMA ELÉCTRICO CENTRAL DE CÁMARAS COMUNA DE LLAY LLAY</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-08-03T15:04:02.44</t>
+          <t>2026-08-17T15:00:00</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -13953,7 +13961,7 @@
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr"/>
@@ -13961,12 +13969,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>4487-29-LE26</t>
+          <t>407-101-LP26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN LICEO POLIVALENTE LA FRONTERA NEGRET</t>
+          <t>MANTENIMIENTO PREVENTIVO Y REPARATIVO SIN REPUESTOS PARA ECÓGRAFOS</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -13974,7 +13982,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-08-03T15:01:00</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -14091,20 +14099,20 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1063538-165-LP26</t>
+          <t>4366-22-LP26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CONVENIO MANTENIMIENTO DE EQUIPOS MEDICOS</t>
+          <t>Rotura y reposición pavimento asfáltico</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-08-03T16:15:00</t>
+          <t>2026-08-03T15:04:02.44</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -14221,20 +14229,20 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1063538-185-LP26</t>
+          <t>4487-29-LE26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO SISTEMA GASES CLINICOS</t>
+          <t>CONSERVACIÓN LICEO POLIVALENTE LA FRONTERA NEGRET</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-08-14T15:15:00</t>
+          <t>2026-08-03T15:01:00</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -14343,7 +14351,7 @@
       <c r="AB105" t="inlineStr"/>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr"/>
@@ -14351,12 +14359,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1344402-6-E226</t>
+          <t>1063538-165-LP26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MANTENCIÓN Y DIAGNÓSTICO CÁMARAS DE CONSERVACIÓN</t>
+          <t>CONVENIO MANTENIMIENTO DE EQUIPOS MEDICOS</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -14364,7 +14372,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-08-03T16:15:00</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -14481,20 +14489,20 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1057545-85-LE26</t>
+          <t>1063538-185-LP26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Contratación de servicios para convenio suministro de servicio de mantenimiento al sistema de detección y extinción de incendios para los Hospitales de Corral y Lanco</t>
+          <t>MANTENIMIENTO SISTEMA GASES CLINICOS</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-08-03T15:01:00</t>
+          <t>2026-08-14T15:15:00</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -14603,7 +14611,7 @@
       <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr"/>
@@ -14611,20 +14619,20 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1263503-2-O126</t>
+          <t>1344402-6-E226</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA II</t>
+          <t>MANTENCIÓN Y DIAGNÓSTICO CÁMARAS DE CONSERVACIÓN</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-08-03T11:03:43.517</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -14741,20 +14749,20 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>633-43-L126</t>
+          <t>1057545-85-LE26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>CURSO DE CAPACITACIÓN EN PUEBLOS INDÍGENAS</t>
+          <t>Contratación de servicios para convenio suministro de servicio de mantenimiento al sistema de detección y extinción de incendios para los Hospitales de Corral y Lanco</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-08-10T19:00:00</t>
+          <t>2026-08-03T15:01:00</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -14772,12 +14780,12 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -14857,13 +14865,13 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr"/>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD109" t="inlineStr"/>
@@ -14871,20 +14879,20 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>934-11-LE26</t>
+          <t>1263503-2-O126</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SERVICIO DE GUARDIAS IND REGION DE LOS LAGOS</t>
+          <t>CONSERVACIÓN DE VÍAS 2026-2029, ARICA, ETAPA II</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-03T11:03:43.517</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -14902,12 +14910,12 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial)</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -14987,7 +14995,7 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr"/>
@@ -15001,12 +15009,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>935-17-LE26</t>
+          <t>633-43-L126</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>INDUMENTARIA DEPORTIVA SNCD IND XII REGION</t>
+          <t>CURSO DE CAPACITACIÓN EN PUEBLOS INDÍGENAS</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -15014,7 +15022,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-14T09:00:00</t>
+          <t>2026-08-10T19:00:00</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -15123,7 +15131,7 @@
       <c r="AB111" t="inlineStr"/>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AD111" t="inlineStr"/>
@@ -15131,12 +15139,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2332-78-L126</t>
+          <t>934-11-LE26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SERVICIOS DE CONSERVACIÓN DE INFRAESTRUCTURA DEL SAR ALERCE</t>
+          <t>SERVICIO DE GUARDIAS IND REGION DE LOS LAGOS</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -15162,12 +15170,12 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -15247,7 +15255,7 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr"/>
@@ -15261,12 +15269,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2765-44-E226</t>
+          <t>935-17-LE26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO CENTRO COMUNITARIO SERGI</t>
+          <t>INDUMENTARIA DEPORTIVA SNCD IND XII REGION</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -15274,7 +15282,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-08-10T16:23:00</t>
+          <t>2026-08-14T09:00:00</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -15292,12 +15300,12 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -15377,13 +15385,13 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr"/>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD113" t="inlineStr"/>
@@ -15391,12 +15399,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3390-21-LE26</t>
+          <t>2332-78-L126</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Materiales para Mantenimiento y Reparaciones.</t>
+          <t>SERVICIOS DE CONSERVACIÓN DE INFRAESTRUCTURA DEL SAR ALERCE</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -15404,7 +15412,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-08-03T15:57:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -15521,20 +15529,20 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2467-79-LE26</t>
+          <t>2765-44-E226</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE CAMARAS DE SEGURIDAD PARA RECAMBIO</t>
+          <t>SERVICIO DE MANTENIMIENTO CENTRO COMUNITARIO SERGI</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-03T15:20:00</t>
+          <t>2026-08-10T16:23:00</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -15643,7 +15651,7 @@
       <c r="AB115" t="inlineStr"/>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AD115" t="inlineStr"/>
@@ -15651,20 +15659,20 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3399-17-L126</t>
+          <t>3390-21-LE26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Servicio de mantenimiento para el mini bus Merces Benz Sprinter del Regimiento N° 16 Talca.</t>
+          <t>Materiales para Mantenimiento y Reparaciones.</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-07-30T15:56:00</t>
+          <t>2026-08-03T15:57:00</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -15773,7 +15781,7 @@
       <c r="AB116" t="inlineStr"/>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr"/>
@@ -15781,20 +15789,20 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3482-6-LE26</t>
+          <t>2467-79-LE26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Mantenimiento y Reparación de Baño.</t>
+          <t>ADQUISICIÓN DE CAMARAS DE SEGURIDAD PARA RECAMBIO</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-08-10T16:00:00</t>
+          <t>2026-08-03T15:20:00</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -15903,7 +15911,7 @@
       <c r="AB117" t="inlineStr"/>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD117" t="inlineStr"/>
@@ -15911,20 +15919,20 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2793-104-LE26</t>
+          <t>3399-17-L126</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE EQUIPOS Y SISTEMAS CLIMATIZACION</t>
+          <t>Servicio de mantenimiento para el mini bus Merces Benz Sprinter del Regimiento N° 16 Talca.</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-08-03T15:01:00</t>
+          <t>2026-07-30T15:56:00</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -16033,7 +16041,7 @@
       <c r="AB118" t="inlineStr"/>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD118" t="inlineStr"/>
@@ -16041,12 +16049,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2981-204-LE26</t>
+          <t>3482-6-LE26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO DE CALDERAS</t>
+          <t>Mantenimiento y Reparación de Baño.</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -16054,7 +16062,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-08-14T15:00:00</t>
+          <t>2026-08-10T16:00:00</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -16163,7 +16171,7 @@
       <c r="AB119" t="inlineStr"/>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr"/>
@@ -16171,20 +16179,20 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3084-15-R126</t>
+          <t>2793-104-LE26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE LICENCIAS OFFICE LTSC PRO PLUS 2024 LICENCIAS MICROSOFT WINDOWS 11 PRO LICENCIAS WINDOWS EXCHANGE SERVER 2019 LICENCIAS WINDOWS SERVER 2025 STANDARD 16 CORES ESP Y LICENCIAS EXCHANGE SERVER STANDARD 2019 CAL SU EQUIVALENTE TÉCNICO O SU</t>
+          <t>MANTENIMIENTO DE EQUIPOS Y SISTEMAS CLIMATIZACION</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-06-03T15:00:00</t>
+          <t>2026-08-03T15:01:00</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -16202,12 +16210,12 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial)</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -16287,13 +16295,13 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr"/>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr"/>
@@ -16301,20 +16309,20 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3693-141-CO26</t>
+          <t>2981-204-LE26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN Y HABILITACIÓN SALAS DE BOMBAS COMPLEJO EDUCACIONAL CLARA SOLOVERA COLEGIO EL QUISCO Y ESCUELA POETA NERUDA</t>
+          <t>SERVICIO DE MANTENIMIENTO DE CALDERAS</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-14T15:00:00</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -16423,7 +16431,7 @@
       <c r="AB121" t="inlineStr"/>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD121" t="inlineStr"/>
@@ -16431,20 +16439,20 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>407-86-LE26</t>
+          <t>3084-15-R126</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO PREVENTIVO Y REPARATIVO SIN REPUESTOS PARA AUTOCLAVE</t>
+          <t>“ADQUISICIÓN DE LICENCIAS OFFICE LTSC PRO PLUS 2024 LICENCIAS MICROSOFT WINDOWS 11 PRO LICENCIAS WINDOWS EXCHANGE SERVER 2019 LICENCIAS WINDOWS SERVER 2025 STANDARD 16 CORES ESP Y LICENCIAS EXCHANGE SERVER STANDARD 2019 CAL SU EQUIVALENTE TÉCNICO O SU</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-08-03T10:53:14.54</t>
+          <t>2026-06-03T15:00:00</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -16462,12 +16470,12 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -16547,13 +16555,13 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr"/>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD122" t="inlineStr"/>
@@ -16561,20 +16569,20 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1798-5-LE26</t>
+          <t>3693-141-CO26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Servicio de Mantenimiento de Red eléctrica y otros</t>
+          <t>CONSERVACIÓN Y HABILITACIÓN SALAS DE BOMBAS COMPLEJO EDUCACIONAL CLARA SOLOVERA COLEGIO EL QUISCO Y ESCUELA POETA NERUDA</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-07-24T15:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -16683,7 +16691,7 @@
       <c r="AB123" t="inlineStr"/>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr"/>
@@ -16691,20 +16699,20 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1951-31-LE26</t>
+          <t>407-86-LE26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO CORRECTIVO EQUIPOS REFRIG</t>
+          <t>SERVICIO DE MANTENIMIENTO PREVENTIVO Y REPARATIVO SIN REPUESTOS PARA AUTOCLAVE</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-08-03T15:31:00</t>
+          <t>2026-08-03T10:53:14.54</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -16821,20 +16829,20 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2328-44-LE26</t>
+          <t>1798-5-LE26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA E-472026 “ADQUISICION DE MATERIALES ELECTRICOS PARA LA ESPECIALIDAD DE ELECTRICIDAD TP 2024 LICEO INDUSTRIAL PUERTO MONTT”</t>
+          <t>Servicio de Mantenimiento de Red eléctrica y otros</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-08-03T15:03:00</t>
+          <t>2026-07-24T15:00:00</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -16852,12 +16860,12 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial)</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -16937,13 +16945,13 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr"/>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AD125" t="inlineStr"/>
@@ -16951,20 +16959,20 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>638-15-LE26</t>
+          <t>1951-31-LE26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>REPARACIÓN MANTENIMIENTO Y NORMALIZACIÓN QUINCHO</t>
+          <t>MANTENIMIENTO PREVENTIVO CORRECTIVO EQUIPOS REFRIG</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-07-20T15:30:00</t>
+          <t>2026-08-03T15:31:00</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -17073,7 +17081,7 @@
       <c r="AB126" t="inlineStr"/>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr"/>
@@ -17081,20 +17089,20 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>898-42-R126</t>
+          <t>2328-44-LE26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO CENTRALES DE GASES CLINICOS</t>
+          <t>LICITACIÓN PÚBLICA E-472026 “ADQUISICION DE MATERIALES ELECTRICOS PARA LA ESPECIALIDAD DE ELECTRICIDAD TP 2024 LICEO INDUSTRIAL PUERTO MONTT”</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-03-23T15:00:00</t>
+          <t>2026-08-03T15:03:00</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -17112,12 +17120,12 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -17197,13 +17205,13 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr"/>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD127" t="inlineStr"/>
@@ -17211,12 +17219,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>3296-19-LE25</t>
+          <t>638-15-LE26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Contratación AITO conservación camino no enrolados 8 sectores rurales Curaco de Vélez.</t>
+          <t>REPARACIÓN MANTENIMIENTO Y NORMALIZACIÓN QUINCHO</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -17224,7 +17232,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-01-08T19:55:00</t>
+          <t>2026-07-20T15:30:00</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -17282,7 +17290,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>Certificación SEC (Chile)</t>
+          <t>Normativa estándar de licitación</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
@@ -17333,7 +17341,7 @@
       <c r="AB128" t="inlineStr"/>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AD128" t="inlineStr"/>
@@ -17341,20 +17349,20 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>5908-25-LP26</t>
+          <t>898-42-R126</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>REPOSICIÓN ESCALERAS PÚBLICAS LOCALIDAD DE SIBAYA COMUNA DE HUARA</t>
+          <t>MANTENIMIENTO PREVENTIVO CENTRALES DE GASES CLINICOS</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-08-03T16:00:00</t>
+          <t>2026-03-23T15:00:00</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -17463,7 +17471,7 @@
       <c r="AB129" t="inlineStr"/>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr"/>
@@ -17471,20 +17479,20 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>812799-44-LP26</t>
+          <t>3296-19-LE25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>REPOSICIÓN CENTRO COMUNITARIO 5 COMUNA DE MEJILLONES C.BIP 40074392-0</t>
+          <t>Contratación AITO conservación camino no enrolados 8 sectores rurales Curaco de Vélez.</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-08-31T15:00:00</t>
+          <t>2026-01-08T19:55:00</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -17542,7 +17550,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>Normativa estándar de licitación</t>
+          <t>Certificación SEC (Chile)</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
@@ -17593,7 +17601,7 @@
       <c r="AB130" t="inlineStr"/>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AD130" t="inlineStr"/>
@@ -17601,20 +17609,20 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>821-8-O126</t>
+          <t>5908-25-LP26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Reposición Cuartel BICRIM Ovalle</t>
+          <t>REPOSICIÓN ESCALERAS PÚBLICAS LOCALIDAD DE SIBAYA COMUNA DE HUARA</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-08-03T08:26:23.16</t>
+          <t>2026-08-03T16:00:00</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -17731,20 +17739,20 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>932-21-LE26</t>
+          <t>812799-44-LP26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Mantenimiento preventivo y correctivo presurizador</t>
+          <t>REPOSICIÓN CENTRO COMUNITARIO 5 COMUNA DE MEJILLONES C.BIP 40074392-0</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-08-03T16:00:00</t>
+          <t>2026-08-31T15:00:00</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -17853,7 +17861,7 @@
       <c r="AB132" t="inlineStr"/>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr"/>
@@ -17861,20 +17869,20 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>948354-72-LE26</t>
+          <t>821-8-O126</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE MANTENIMIENTO DE EQUIPO DE RAYOS X DEL HOSPITAL DIPRECA</t>
+          <t>Reposición Cuartel BICRIM Ovalle</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-08-03T15:56:05.627</t>
+          <t>2026-08-03T08:26:23.16</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -17991,20 +17999,20 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4483-15-LR26</t>
+          <t>932-21-LE26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>REPOSICION CUARTEL GENERAL 1° COMPAÑIA DE BOMBEROS TIERRA AMARILLA</t>
+          <t>Mantenimiento preventivo y correctivo presurizador</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-06-30T15:30:00</t>
+          <t>2026-08-03T16:00:00</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -18113,7 +18121,7 @@
       <c r="AB134" t="inlineStr"/>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD134" t="inlineStr"/>
@@ -18121,20 +18129,20 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>4494-47-LE26</t>
+          <t>948354-72-LE26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN ESCUELA EDUARDO CAMPBELL PENCO</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE MANTENIMIENTO DE EQUIPO DE RAYOS X DEL HOSPITAL DIPRECA</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-08-18T15:00:00</t>
+          <t>2026-08-03T15:56:05.627</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -18243,7 +18251,7 @@
       <c r="AB135" t="inlineStr"/>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr"/>
@@ -18251,20 +18259,20 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>584264-35-LR26</t>
+          <t>4483-15-LR26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SUM.SEÑALES DE TRANSITO DEMARCACIÓN INDEPENDENCIA</t>
+          <t>REPOSICION CUARTEL GENERAL 1° COMPAÑIA DE BOMBEROS TIERRA AMARILLA</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-04T15:05:00</t>
+          <t>2026-06-30T15:30:00</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -18282,12 +18290,12 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial)</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -18367,13 +18375,13 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AD136" t="inlineStr"/>
@@ -18381,12 +18389,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>608897-45-LE26</t>
+          <t>4494-47-LE26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SISTEMATIZACIÓN DE INFORMACIÓN PARA LA IDENTIFICACIÓN DE PRIORIDADES DE CONSERVACIÓN MARINA PARA EL DISEÑO DE UNA RED DE ÁREAS MARINAS PROTEGIDAS EN LAS ECORREGIONES HUMBOLDTIANA CHILE CENTRAL ARAUCANA CHILOENSE Y CANALESFIORDOS DEL SUR DE CHILE</t>
+          <t>CONSERVACIÓN ESCUELA EDUARDO CAMPBELL PENCO</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -18394,7 +18402,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-08-13T16:00:00</t>
+          <t>2026-08-18T15:00:00</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -18503,7 +18511,7 @@
       <c r="AB137" t="inlineStr"/>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr"/>
@@ -18511,12 +18519,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>610-13-LP26</t>
+          <t>584264-35-LR26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Determinación del Estándar Metodológico para el Cálculo de Rotura y Reposición de Pavimentos en Redes de Distribución</t>
+          <t>SUM.SEÑALES DE TRANSITO DEMARCACIÓN INDEPENDENCIA</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -18524,7 +18532,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-08-21T15:00:00</t>
+          <t>2026-09-04T15:05:00</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -18542,12 +18550,12 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -18627,13 +18635,13 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr"/>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD138" t="inlineStr"/>
@@ -18641,20 +18649,20 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2328-43-LE26</t>
+          <t>608897-45-LE26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA E-502026  “ADQUISICION DE EQUIPAMIENTO PARA LA ESPECIALIDAD DE MECANICA INDUSTRIAL DEL LICEO INDUSTRIAL PUERTO MONTT FONDO TP 2024”</t>
+          <t>SISTEMATIZACIÓN DE INFORMACIÓN PARA LA IDENTIFICACIÓN DE PRIORIDADES DE CONSERVACIÓN MARINA PARA EL DISEÑO DE UNA RED DE ÁREAS MARINAS PROTEGIDAS EN LAS ECORREGIONES HUMBOLDTIANA CHILE CENTRAL ARAUCANA CHILOENSE Y CANALESFIORDOS DEL SUR DE CHILE</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-08-03T15:52:00</t>
+          <t>2026-08-13T16:00:00</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -18672,12 +18680,12 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial)</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -18757,13 +18765,13 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr"/>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD139" t="inlineStr"/>
@@ -18771,20 +18779,20 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>3080-2-L126</t>
+          <t>610-13-LP26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE SERVICIO POR REPARACIÓN Y MANTENIMIENTO EDIFICIO MICALVI </t>
+          <t>Determinación del Estándar Metodológico para el Cálculo de Rotura y Reposición de Pavimentos en Redes de Distribución</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-21T15:00:00</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -18893,7 +18901,7 @@
       <c r="AB140" t="inlineStr"/>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD140" t="inlineStr"/>
@@ -18901,12 +18909,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3436-86-L126</t>
+          <t>2328-43-LE26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Mantenimiento de equipos de rancho Ítem 22.06.999 SIC 349184</t>
+          <t>LICITACIÓN PÚBLICA E-502026  “ADQUISICION DE EQUIPAMIENTO PARA LA ESPECIALIDAD DE MECANICA INDUSTRIAL DEL LICEO INDUSTRIAL PUERTO MONTT FONDO TP 2024”</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -18914,7 +18922,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-08-03T15:10:00</t>
+          <t>2026-08-03T15:52:00</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -18932,12 +18940,12 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -19017,7 +19025,7 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr"/>
@@ -19031,20 +19039,20 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>618472-3-L126</t>
+          <t>3080-2-L126</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Servicio de mantenimiento, reparación y repuestos de Aire Acondicionado.</t>
+          <t xml:space="preserve">ADQUISICIÓN DE SERVICIO POR REPARACIÓN Y MANTENIMIENTO EDIFICIO MICALVI </t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-08-12T08:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -19153,7 +19161,7 @@
       <c r="AB142" t="inlineStr"/>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD142" t="inlineStr"/>
@@ -19161,12 +19169,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>707426-25-LP26</t>
+          <t>3436-86-L126</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>REPOSICIÓN CUBIERTA Y SIST. ELECT. JI TIA NORA.</t>
+          <t>Mantenimiento de equipos de rancho Ítem 22.06.999 SIC 349184</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -19174,7 +19182,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00</t>
+          <t>2026-08-03T15:10:00</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -19291,20 +19299,20 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>740-12-LE26</t>
+          <t>618472-3-L126</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SERVICIO DE CATERING EN LA REGIÓN DEL MAULE INDAP</t>
+          <t>Servicio de mantenimiento, reparación y repuestos de Aire Acondicionado.</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-08-12T08:00:00</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -19322,12 +19330,12 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial)</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -19407,13 +19415,13 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr"/>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD144" t="inlineStr"/>
@@ -19421,20 +19429,20 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>761391-107-L126</t>
+          <t>707426-25-LP26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>DE/56/GUB/CURSO DE MANTENIMIENTO DE SISTEMAS DE REFRIGERACIÓN Y MANTENIMIENTO DE CALDERAS</t>
+          <t>REPOSICIÓN CUBIERTA Y SIST. ELECT. JI TIA NORA.</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-07-21T15:00:00</t>
+          <t>2026-08-03T15:00:00</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -19543,7 +19551,7 @@
       <c r="AB145" t="inlineStr"/>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr"/>
@@ -19551,20 +19559,20 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>802-11-LE26</t>
+          <t>740-12-LE26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Difusión y validación de un programa de Magíster en lengua y cultura indígena</t>
+          <t>SERVICIO DE CATERING EN LA REGIÓN DEL MAULE INDAP</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-06-23T10:00:00</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -19673,7 +19681,7 @@
       <c r="AB146" t="inlineStr"/>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD146" t="inlineStr"/>
@@ -19681,20 +19689,20 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>826-11-O126</t>
+          <t>761391-107-L126</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>AIF OBRA REPOSICIÓN CONSULTORIO LAUTARO Y ADECUACIÓN A CESFAM</t>
+          <t>DE/56/GUB/CURSO DE MANTENIMIENTO DE SISTEMAS DE REFRIGERACIÓN Y MANTENIMIENTO DE CALDERAS</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-08-19T09:00:00</t>
+          <t>2026-07-21T15:00:00</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -19803,7 +19811,7 @@
       <c r="AB147" t="inlineStr"/>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr"/>
@@ -19811,20 +19819,20 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>948354-112-LE26</t>
+          <t>802-11-LE26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE MANTENIMIENTO CON REPUESTOS INCLUIDOS DE MÁQUINAS DE DIÁLISIS DEL HOSPITAL DIPRECA</t>
+          <t>Difusión y validación de un programa de Magíster en lengua y cultura indígena</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-08-03T16:00:00</t>
+          <t>2026-06-23T10:00:00</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -19842,12 +19850,12 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -19927,13 +19935,13 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr"/>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr"/>
@@ -19941,20 +19949,20 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1389488-17-LP26</t>
+          <t>826-11-O126</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUMINISTRO DE INDUMENTARIA ARTÍCULOS DEPORTIVOS   </t>
+          <t>AIF OBRA REPOSICIÓN CONSULTORIO LAUTARO Y ADECUACIÓN A CESFAM</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-06-04T16:37:00</t>
+          <t>2026-08-19T09:00:00</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -19972,12 +19980,12 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial)</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -20057,13 +20065,13 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr"/>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr"/>
@@ -20071,12 +20079,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2403-52-LP26</t>
+          <t>948354-112-LE26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Reposición calzada pasaje Maracaibo</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE MANTENIMIENTO CON REPUESTOS INCLUIDOS DE MÁQUINAS DE DIÁLISIS DEL HOSPITAL DIPRECA</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -20084,7 +20092,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-08-03T15:30:00</t>
+          <t>2026-08-03T16:00:00</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -20201,20 +20209,20 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>3565-54-LE26</t>
+          <t>1389488-17-LP26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>MATRERIALES PARA REPOSICION PASARELAS</t>
+          <t xml:space="preserve">SUMINISTRO DE INDUMENTARIA ARTÍCULOS DEPORTIVOS   </t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-08-14T12:24:00</t>
+          <t>2026-06-04T16:37:00</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -20232,12 +20240,12 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -20317,13 +20325,13 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr"/>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD151" t="inlineStr"/>
@@ -20331,20 +20339,20 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>4261-4-LE26</t>
+          <t>2403-52-LP26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MTS Conservación CDI España Comuna de Angol</t>
+          <t>Reposición calzada pasaje Maracaibo</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-08-03T16:20:14.27</t>
+          <t>2026-08-03T15:30:00</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -20461,20 +20469,20 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>545598-24-LE26</t>
+          <t>3565-54-LE26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE OXÍGENO MEDICINAL Y GASES CLÍNICOS CON CILINDROS EN ARRIENDO</t>
+          <t>MATRERIALES PARA REPOSICION PASARELAS</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-07-17T15:04:00</t>
+          <t>2026-08-14T12:24:00</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -20492,12 +20500,12 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial)</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -20577,13 +20585,13 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr"/>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD153" t="inlineStr"/>
@@ -20591,20 +20599,20 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>584105-14-LP26</t>
+          <t>4261-4-LE26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>INCORPORACIÓN COMPONENTE INDÍGENA EN LA PLANIFICACIÓN ENERGÉTICA Y RESILIENCIA ENERGÉTICA EN RAPA NUI EN CUMPLIMIENTO CON EL PLAN SECTORIAL DE MITIGACIÓN Y DE ADAPTACIÓN AL CAMBIO CLIMÁTICO EN ENERGÍA</t>
+          <t>MTS Conservación CDI España Comuna de Angol</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-08-24T15:01:00</t>
+          <t>2026-08-03T16:20:14.27</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -20622,12 +20630,12 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / IND</t>
+          <t>Iluminación General / Industrial</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>ActiStar / CoreLine (Industrial)</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -20662,7 +20670,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>Certificación SEC (Chile)</t>
+          <t>Normativa estándar de licitación</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
@@ -20707,13 +20715,13 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr"/>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD154" t="inlineStr"/>
@@ -20721,20 +20729,20 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>697057-29-LE26</t>
+          <t>545598-24-LE26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Reposición cubierta de la Fiscalía de Pichilemu</t>
+          <t>CONVENIO DE SUMINISTRO DE OXÍGENO MEDICINAL Y GASES CLÍNICOS CON CILINDROS EN ARRIENDO</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-03T11:00:00</t>
+          <t>2026-07-17T15:04:00</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -20752,12 +20760,12 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Iluminación General / Industrial</t>
+          <t>Iluminación Deportiva / IND</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>ActiStar / CoreLine (Industrial)</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -20837,13 +20845,13 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr"/>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD155" t="inlineStr"/>
@@ -20851,20 +20859,20 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>359-91-LE26</t>
+          <t>584105-14-LP26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ADECUACIÓN DE RECINTOS PARA INSTALACIÓN DE TOMÓGRAFO COMPUTARIZADO EN EL INSTITUTO NACIONAL DEL CÁNCER</t>
+          <t>INCORPORACIÓN COMPONENTE INDÍGENA EN LA PLANIFICACIÓN ENERGÉTICA Y RESILIENCIA ENERGÉTICA EN RAPA NUI EN CUMPLIMIENTO CON EL PLAN SECTORIAL DE MITIGACIÓN Y DE ADAPTACIÓN AL CAMBIO CLIMÁTICO EN ENERGÍA</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-08-03T16:00:00</t>
+          <t>2026-08-24T15:01:00</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -20882,73 +20890,333 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t>Iluminación Deportiva / IND</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Competencia Local / Alternativa</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Evaluada según criterios técnicos y económicos.</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>No especificado en bases</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>No especificado en bases</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>IP66 Requerido</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>IK08 Requerido</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>Certificación SEC (Chile)</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Pesos Chilenos (CLP)</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>No se exige visita a terreno obligatoria</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Garantía de seriedad de oferta y fiel cumplimiento estándar</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Conforme a cronograma oficial de bases</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>Estándar 5 Años</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>Aplicación de multas por atraso estándar MOP/Mercado Público</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>Potencia (No especificado en bases): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr"/>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>697057-29-LE26</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Reposición cubierta de la Fiscalía de Pichilemu</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>5</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-09-03T11:00:00</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>No especificado / En proceso</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
           <t>Iluminación General / Industrial</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>ActiStar / CoreLine (Industrial)</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Competencia Local / Alternativa</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>Evaluada según criterios técnicos y económicos.</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>No especificado en bases</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>No especificado en bases</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>IP66 Requerido</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>IK08 Requerido</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>Normativa estándar de licitación</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>Control autónomo o estándar</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Pesos Chilenos (CLP)</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>No se exige visita a terreno obligatoria</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Garantía de seriedad de oferta y fiel cumplimiento estándar</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Conforme a cronograma oficial de bases</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Estándar 5 Años</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>Aplicación de multas por atraso estándar MOP/Mercado Público</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr"/>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>359-91-LE26</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>ADECUACIÓN DE RECINTOS PARA INSTALACIÓN DE TOMÓGRAFO COMPUTARIZADO EN EL INSTITUTO NACIONAL DEL CÁNCER</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>6</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:00:00</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>No especificado / En proceso</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Iluminación General / Industrial</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
         <is>
           <t>ActiStar / CoreLine (Industrial y General)</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr">
+      <c r="L158" t="inlineStr">
         <is>
           <t>Competencia Local / Alternativa</t>
         </is>
       </c>
-      <c r="M156" t="inlineStr">
+      <c r="M158" t="inlineStr">
         <is>
           <t>Evaluada según criterios técnicos, económicos y plazo.</t>
         </is>
       </c>
-      <c r="N156" t="inlineStr">
+      <c r="N158" t="inlineStr">
         <is>
           <t>No especificado en bases</t>
         </is>
       </c>
-      <c r="O156" t="inlineStr">
+      <c r="O158" t="inlineStr">
         <is>
           <t>No especificado en bases</t>
         </is>
       </c>
-      <c r="P156" t="inlineStr">
+      <c r="P158" t="inlineStr">
         <is>
           <t>IP66 Requerido (Estándar)</t>
         </is>
       </c>
-      <c r="Q156" t="inlineStr">
+      <c r="Q158" t="inlineStr">
         <is>
           <t>IK08 Requerido (Estándar)</t>
         </is>
       </c>
-      <c r="R156" t="inlineStr">
+      <c r="R158" t="inlineStr">
         <is>
           <t>Normativa estándar / DS1 aplicable</t>
         </is>
       </c>
-      <c r="S156" t="inlineStr">
+      <c r="S158" t="inlineStr">
         <is>
           <t>Control autónomo o estándar</t>
         </is>
       </c>
-      <c r="T156" t="inlineStr"/>
-      <c r="U156" t="inlineStr"/>
-      <c r="V156" t="inlineStr"/>
-      <c r="W156" t="inlineStr"/>
-      <c r="X156" t="inlineStr"/>
-      <c r="Y156" t="inlineStr"/>
-      <c r="Z156" t="inlineStr">
+      <c r="T158" t="inlineStr"/>
+      <c r="U158" t="inlineStr"/>
+      <c r="V158" t="inlineStr"/>
+      <c r="W158" t="inlineStr"/>
+      <c r="X158" t="inlineStr"/>
+      <c r="Y158" t="inlineStr"/>
+      <c r="Z158" t="inlineStr">
         <is>
           <t>Cumple Totalmente</t>
         </is>
       </c>
-      <c r="AA156" t="inlineStr">
+      <c r="AA158" t="inlineStr">
         <is>
           <t>Luminaria de uso general/industrial: Portafolio CoreLine / ActiStar cubre los requerimientos técnicos base.</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr"/>
-      <c r="AC156" t="inlineStr"/>
-      <c r="AD156" t="inlineStr">
+      <c r="AB158" t="inlineStr"/>
+      <c r="AC158" t="inlineStr"/>
+      <c r="AD158" t="inlineStr">
         <is>
           <t>ActiStar / CoreLine: Alta eficiencia industrial, IP65/66, driver LED programable.</t>
         </is>

--- a/agliluz/historial_licitaciones.xlsx
+++ b/agliluz/historial_licitaciones.xlsx
@@ -583,20 +583,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3981-21-LE26</t>
+          <t>771555-9-LP26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INSTALACIÓN LUMINARIAS RUTA I-512 SECTOR LA CAPILLA COMUNA DE PAREDONES</t>
+          <t>Mejoramiento Cancha de Futbol Fundina Norte RH</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-05T09:12:26.2</t>
+          <t>2026-08-05T10:00:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -618,12 +618,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Proyectores de Área / General</t>
+          <t>Iluminación Deportiva / Canchas</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Proyectores de Área / CoreLine</t>
+          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
+          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -717,20 +717,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>771555-9-LP26</t>
+          <t>3981-21-LE26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mejoramiento Cancha de Futbol Fundina Norte RH</t>
+          <t>INSTALACIÓN LUMINARIAS RUTA I-512 SECTOR LA CAPILLA COMUNA DE PAREDONES</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-05T10:00:00</t>
+          <t>2026-08-05T09:12:26.2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva / Canchas</t>
+          <t>Proyectores de Área / General</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports (Proyectores Deportivos)</t>
+          <t>Proyectores de Área / CoreLine</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Potencia (100W - 250W (Estimado Bases)): Cubierta por familia Arena X con conectividad Interact Sports y cumplimiento DS1.</t>
+          <t>Portafolio industrial ActiStar / CoreLine cubre requerimientos base.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>

--- a/agliluz/historial_licitaciones.xlsx
+++ b/agliluz/historial_licitaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,12 +528,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3981-21-LE26</t>
+          <t>3668-13-LP26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INSTALACIÓN LUMINARIAS RUTA I-512 SECTOR LA CAPILLA COMUNA DE PAREDONES</t>
+          <t>SERVICIO DE MANTENCIÓN Y REPARACIÓN DEL ALUMBRADO PÚBLICO VIAL Y PEATONAL COMUNA DE CALERA DE TANGO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Normativa DS1 / Estándar</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -600,13 +600,268 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Score: 70 | +35 (luminaria) | +35 (luminarias) | Luminarias detectadas: 0</t>
+          <t>Score: 45 | +30 (alumbrado) | +15 (vial) | Luminarias detectadas: 0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3333-36-LE26</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE INSUMOS PARA RESPOSICIÓN DE LUMINARIAS OLMUÉ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Iluminación Vial / Pública</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>RoadFlair / Xceed Pro + Interact City</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>No especificado en bases</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>No especificado en bases</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>IP66 Requerido</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>IK08 Requerido</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Control estándar / Autónomo</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Normativa DS1 / Estándar</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>En curso / Vigente</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>70</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente (Alta Prioridad)</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Score: 70 | +35 (luminaria) | +35 (luminarias) | Luminarias detectadas: 0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>4072-28-LP26</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CONST. SISTEMA DE ILUMINACIÓN ESTADIO ESTACION YUM</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Iluminación Deportiva</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Arena X + Interact Sports</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>No especificado en bases</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>No especificado en bases</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>IP66 Requerido</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>IK08 Requerido</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Control estándar / Autónomo</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Normativa DS1 / Estándar</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>En curso / Vigente</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>50</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente (Alta Prioridad)</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Score: 50 | +30 (iluminación) | +20 (estadio) | Luminarias detectadas: 0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2277-21-LP26</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>INSTALACION DE LUMINARIAS PEATONALES EN VEREDAS AV. TENIENTE CRUZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Iluminación Vial / Pública</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RoadFlair / Xceed Pro + Interact City</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>No especificado en bases</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>No especificado en bases</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>IP66 Requerido</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>IK08 Requerido</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Control estándar / Autónomo</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Normativa DS1 / Estándar</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>En curso / Vigente</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>70</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente (Alta Prioridad)</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Score: 70 | +35 (luminaria) | +35 (luminarias) | Luminarias detectadas: 0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>

--- a/agliluz/historial_licitaciones.xlsx
+++ b/agliluz/historial_licitaciones.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,192 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CodigoExterno</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Categoria_Proyecto</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Signify_Equivalente</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cantidad_Unidades</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Requerimiento_Potencia</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Requerimiento_Flujo_Luminoso</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Requerimiento_IP</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Requerimiento_IK</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Sistemas_Control_Telegestion</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Certificaciones_Exigidas</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Proveedor_Adjudicado</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Monto_Propuesta_CLP</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Monto_Adjudicado_CLP</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Score_Relevancia</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Estado_Cumplimiento_Signify</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Analisis_Brecha_Tecnica</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha_Creacion</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha_Cierre</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>557639-64-LE26</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pantallas y Proyectores Establecimientos Cormun</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Iluminación Vial / Pública</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>RoadFlair / Xceed Pro + Interact City</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No especificado en bases</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>No especificado en bases</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>IP66 Requerido</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>IK08 Requerido</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Control estándar / Autónomo</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Normativa DS1 / Estándar</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>En curso / Vigente</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>50</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente (Alta Prioridad)</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Score: 50 | +25 (proyector) | +25 (proyectores) | Luminarias detectadas: 0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/agliluz/historial_licitaciones.xlsx
+++ b/agliluz/historial_licitaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,12 +528,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>557639-64-LE26</t>
+          <t>659-9-LE26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pantallas y Proyectores Establecimientos Cormun</t>
+          <t>SERVICIO DE PROVISIÓN E INSTALACIÓN DE LUMINARIAS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -600,13 +600,98 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Score: 50 | +25 (proyector) | +25 (proyectores) | Luminarias detectadas: 0</t>
+          <t>Score: 70 | +35 (luminaria) | +35 (luminarias) | Luminarias detectadas: 0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2791-22-LE26</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE PROYECTORES Y MÓDULOS INTERACTIVOS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Iluminación Vial / Pública</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>RoadFlair / Xceed Pro + Interact City</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>No especificado en bases</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>No especificado en bases</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>IP66 Requerido</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>IK08 Requerido</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Interact</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Normativa DS1 / Estándar</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>En curso / Vigente</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>50</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente (Alta Prioridad)</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Score: 50 | +25 (proyector) | +25 (proyectores) | Luminarias detectadas: 0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>

--- a/agliluz/historial_licitaciones.xlsx
+++ b/agliluz/historial_licitaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,22 +528,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>659-9-LE26</t>
+          <t>1048-64-LP26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SERVICIO DE PROVISIÓN E INSTALACIÓN DE LUMINARIAS</t>
+          <t>CONSTRUCCION TORRES DE ILUMINACION ESTADIO LAS CRUCES EL TABO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Iluminación Vial / Pública</t>
+          <t>Iluminación Deportiva</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>RoadFlair / Xceed Pro + Interact City</t>
+          <t>Arena X + Interact Sports</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -600,25 +600,25 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Score: 70 | +35 (luminaria) | +35 (luminarias) | Luminarias detectadas: 0</t>
+          <t>Score: 50 | +30 (iluminacion) | +20 (estadio) | Luminarias detectadas: 0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2791-22-LE26</t>
+          <t>1048-36-LP26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE PROYECTORES Y MÓDULOS INTERACTIVOS</t>
+          <t>RECAMBIO E INST. DE LUMINARIAS SECTOR PALO VERDE Y EL FARO EL TABO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -656,12 +656,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Interact</t>
+          <t>Control estándar / Autónomo</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Normativa DS1 / Estándar</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -676,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -685,13 +685,98 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Score: 50 | +25 (proyector) | +25 (proyectores) | Luminarias detectadas: 0</t>
+          <t>Score: 70 | +35 (luminaria) | +35 (luminarias) | Luminarias detectadas: 0</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1048-44-LP26</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION TORRES DE ILUMINACION ESTADIO LAS CRUCES EL TABO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Iluminación Deportiva</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Arena X + Interact Sports</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>No especificado en bases</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>No especificado en bases</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>IP66 Requerido</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>IK08 Requerido</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Control estándar / Autónomo</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Normativa DS1 / Estándar</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>En curso / Vigente</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>50</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente (Alta Prioridad)</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Score: 50 | +30 (iluminacion) | +20 (estadio) | Luminarias detectadas: 0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>

--- a/agliluz/historial_licitaciones.xlsx
+++ b/agliluz/historial_licitaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,22 +528,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1048-64-LP26</t>
+          <t>2788-42-LE26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CONSTRUCCION TORRES DE ILUMINACION ESTADIO LAS CRUCES EL TABO</t>
+          <t>“SUMINISTRO DE NUEVAS LUMINARIAS LED”.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Iluminación Deportiva</t>
+          <t>Iluminación Vial / Pública</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Arena X + Interact Sports</t>
+          <t>RoadFlair / Xceed Pro + Interact City</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -600,183 +600,13 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Score: 50 | +30 (iluminacion) | +20 (estadio) | Luminarias detectadas: 0</t>
+          <t>Score: 70 | +35 (luminaria) | +35 (luminarias) | Luminarias detectadas: 0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1048-36-LP26</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>RECAMBIO E INST. DE LUMINARIAS SECTOR PALO VERDE Y EL FARO EL TABO</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Iluminación Vial / Pública</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>RoadFlair / Xceed Pro + Interact City</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>No especificado en bases</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>No especificado en bases</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>IP66 Requerido</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>IK08 Requerido</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Control estándar / Autónomo</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>En curso / Vigente</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>70</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Cumple Totalmente (Alta Prioridad)</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Score: 70 | +35 (luminaria) | +35 (luminarias) | Luminarias detectadas: 0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1048-44-LP26</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CONSTRUCCION TORRES DE ILUMINACION ESTADIO LAS CRUCES EL TABO</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Iluminación Deportiva</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Arena X + Interact Sports</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>No especificado en bases</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>No especificado en bases</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>IP66 Requerido</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>IK08 Requerido</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Control estándar / Autónomo</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Normativa DS1 / Estándar</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>En curso / Vigente</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>50</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Cumple Totalmente (Alta Prioridad)</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Score: 50 | +30 (iluminacion) | +20 (estadio) | Luminarias detectadas: 0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>

--- a/agliluz/historial_licitaciones.xlsx
+++ b/agliluz/historial_licitaciones.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,192 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CodigoExterno</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Nombre</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Categoria_Proyecto</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Signify_Equivalente</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Cantidad_Unidades</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Requerimiento_Potencia</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Requerimiento_Flujo_Luminoso</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Requerimiento_IP</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Requerimiento_IK</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Sistemas_Control_Telegestion</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Certificaciones_Exigidas</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Proveedor_Adjudicado</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Monto_Propuesta_CLP</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Monto_Adjudicado_CLP</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Score_Relevancia</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Estado_Cumplimiento_Signify</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Analisis_Brecha_Tecnica</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Fecha_Creacion</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Fecha_Cierre</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2788-42-LE26</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>“SUMINISTRO DE NUEVAS LUMINARIAS LED”.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Iluminación Vial / Pública</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>RoadFlair / Xceed Pro + Interact City</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>No especificado en bases</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>No especificado en bases</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>IP66 Requerido</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>IK08 Requerido</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Control estándar / Autónomo</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Normativa DS1 / Estándar</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>En curso / Vigente</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>70</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Cumple Totalmente (Alta Prioridad)</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Score: 70 | +35 (luminaria) | +35 (luminarias) | Luminarias detectadas: 0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/agliluz/historial_licitaciones.xlsx
+++ b/agliluz/historial_licitaciones.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,277 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CodigoExterno</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Categoria_Proyecto</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Signify_Equivalente</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cantidad_Unidades</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Requerimiento_Potencia</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Requerimiento_Flujo_Luminoso</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Requerimiento_IP</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Requerimiento_IK</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Sistemas_Control_Telegestion</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Certificaciones_Exigidas</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Proveedor_Adjudicado</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Monto_Propuesta_CLP</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Monto_Adjudicado_CLP</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Score_Relevancia</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Estado_Cumplimiento_Signify</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Analisis_Brecha_Tecnica</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha_Creacion</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha_Cierre</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>3986-49-LP26</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE ALUMBRADO PÚBLICO RURAL VIAL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Iluminación Vial / Pública</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>RoadFlair / Xceed Pro + Interact City</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No especificado en bases</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>No especificado en bases</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>IP66 Requerido</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>IK08 Requerido</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Control estándar / Autónomo</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Normativa DS1 / Estándar</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>En curso / Vigente</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>45</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente (Alta Prioridad)</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Score: 45 | +30 (alumbrado) | +15 (vial) | Luminarias detectadas: 0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2756-11-LE26</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Adq. Proyectores Multimedia EE.EE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Iluminación Vial / Pública</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>RoadFlair / Xceed Pro + Interact City</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>No especificado en bases</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>No especificado en bases</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>IP66 Requerido</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>IK08 Requerido</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Control estándar / Autónomo</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Normativa DS1 / Estándar</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>En curso / Vigente</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>50</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente (Alta Prioridad)</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Score: 50 | +25 (proyector) | +25 (proyectores) | Luminarias detectadas: 0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/agliluz/historial_licitaciones.xlsx
+++ b/agliluz/historial_licitaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,12 +528,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3986-49-LP26</t>
+          <t>3948-15-LP26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN DE ALUMBRADO PÚBLICO RURAL VIAL</t>
+          <t>CONSTRUCCIÓN LUMINARIAS PUBLICAS SECTORES RURALES</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Normativa DS1 / Estándar</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -600,98 +600,13 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Score: 45 | +30 (alumbrado) | +15 (vial) | Luminarias detectadas: 0</t>
+          <t>Score: 70 | +35 (luminaria) | +35 (luminarias) | Luminarias detectadas: 0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2756-11-LE26</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Adq. Proyectores Multimedia EE.EE</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Iluminación Vial / Pública</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>RoadFlair / Xceed Pro + Interact City</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>No especificado en bases</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>No especificado en bases</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>IP66 Requerido</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>IK08 Requerido</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Control estándar / Autónomo</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Normativa DS1 / Estándar</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>En curso / Vigente</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>50</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Cumple Totalmente (Alta Prioridad)</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Score: 50 | +25 (proyector) | +25 (proyectores) | Luminarias detectadas: 0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>

--- a/agliluz/historial_licitaciones.xlsx
+++ b/agliluz/historial_licitaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,12 +528,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3948-15-LP26</t>
+          <t>721703-25-LE26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN LUMINARIAS PUBLICAS SECTORES RURALES</t>
+          <t>Servicio de arriendo de proyectores y monitores para la Agencia de Calidad de la Educación.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Normativa DS1 / Estándar</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -600,13 +600,98 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Score: 70 | +35 (luminaria) | +35 (luminarias) | Luminarias detectadas: 0</t>
+          <t>Score: 50 | +25 (proyector) | +25 (proyectores) | Luminarias detectadas: 0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2328-73-LE25</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LICITACIÓN PÚBLICA E-462025 “ADQUISICION DE PROYECTORES Y EQUIPOS COMPLEMENTARIOS PARA SALAS DE CLASES ESCUELA ARABE SIRIA ESCUELA RURAL LENCA ESCUELA ARGENTINA LICEO MANUEL MONTT Y ESCUELA ARTURO PRAT DEPENDIENTES DEL D.A.E.M. PUERTO MONTT”</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Iluminación Vial / Pública</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>RoadFlair / Xceed Pro + Interact City</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>No especificado en bases</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>No especificado en bases</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>IP66 Requerido</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>IK08 Requerido</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Control estándar / Autónomo</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Normativa DS1 / Estándar</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>En curso / Vigente</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>50</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Cumple Totalmente (Alta Prioridad)</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Score: 50 | +25 (proyector) | +25 (proyectores) | Luminarias detectadas: 0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
         </is>
       </c>
     </row>

--- a/agliluz/historial_licitaciones.xlsx
+++ b/agliluz/historial_licitaciones.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,277 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CodigoExterno</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Nombre</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Categoria_Proyecto</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Signify_Equivalente</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Cantidad_Unidades</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Requerimiento_Potencia</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Requerimiento_Flujo_Luminoso</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Requerimiento_IP</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Requerimiento_IK</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Sistemas_Control_Telegestion</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Certificaciones_Exigidas</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Proveedor_Adjudicado</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Monto_Propuesta_CLP</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Monto_Adjudicado_CLP</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Score_Relevancia</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Estado_Cumplimiento_Signify</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Analisis_Brecha_Tecnica</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Fecha_Creacion</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Fecha_Cierre</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>721703-25-LE26</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Servicio de arriendo de proyectores y monitores para la Agencia de Calidad de la Educación.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Iluminación Vial / Pública</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>RoadFlair / Xceed Pro + Interact City</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>No especificado en bases</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>No especificado en bases</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>IP66 Requerido</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>IK08 Requerido</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Control estándar / Autónomo</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Normativa DS1 / Estándar</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>En curso / Vigente</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>50</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Cumple Totalmente (Alta Prioridad)</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Score: 50 | +25 (proyector) | +25 (proyectores) | Luminarias detectadas: 0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2328-73-LE25</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>LICITACIÓN PÚBLICA E-462025 “ADQUISICION DE PROYECTORES Y EQUIPOS COMPLEMENTARIOS PARA SALAS DE CLASES ESCUELA ARABE SIRIA ESCUELA RURAL LENCA ESCUELA ARGENTINA LICEO MANUEL MONTT Y ESCUELA ARTURO PRAT DEPENDIENTES DEL D.A.E.M. PUERTO MONTT”</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Iluminación Vial / Pública</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>RoadFlair / Xceed Pro + Interact City</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>No especificado en bases</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>No especificado en bases</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>IP66 Requerido</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>IK08 Requerido</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Control estándar / Autónomo</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Normativa DS1 / Estándar</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>En curso / Vigente</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>50</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Cumple Totalmente (Alta Prioridad)</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Score: 50 | +25 (proyector) | +25 (proyectores) | Luminarias detectadas: 0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>